--- a/IM/202609_Service_Count_Report.xlsx
+++ b/IM/202609_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$61</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="261">
   <si>
     <t>服務次數統計表        篩選月份：202609</t>
   </si>
@@ -125,6 +125,39 @@
     <t>劉柏均</t>
   </si>
   <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>T251000061</t>
+  </si>
+  <si>
+    <t>eS-2510AC 彩色複合機</t>
+  </si>
+  <si>
+    <t>MFP商品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">品興營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區中原街26號旁工地</t>
+  </si>
+  <si>
+    <t>抄表</t>
+  </si>
+  <si>
+    <t>撤機</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>2026-09-01</t>
   </si>
   <si>
@@ -140,9 +173,6 @@
     <t>eS-2520AC 彩色複合機</t>
   </si>
   <si>
-    <t>MFP商品</t>
-  </si>
-  <si>
     <t xml:space="preserve">漢庭營造股份有限公司 </t>
   </si>
   <si>
@@ -152,15 +182,9 @@
     <t>中和</t>
   </si>
   <si>
-    <t>抄表</t>
-  </si>
-  <si>
     <t>Pm</t>
   </si>
   <si>
-    <t>O</t>
-  </si>
-  <si>
     <t>09:50:00</t>
   </si>
   <si>
@@ -179,9 +203,6 @@
     <t>服務</t>
   </si>
   <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
     <t>10:12:00</t>
   </si>
   <si>
@@ -299,6 +320,51 @@
     <t>三重碧華公園</t>
   </si>
   <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>15:32:00</t>
+  </si>
+  <si>
+    <t>THILF03840</t>
+  </si>
+  <si>
+    <t>新北市三重區龍門路176號</t>
+  </si>
+  <si>
+    <t>北縣天龍店</t>
+  </si>
+  <si>
+    <t>13:20:00</t>
+  </si>
+  <si>
+    <t>13:42:00</t>
+  </si>
+  <si>
+    <t>THILF04191</t>
+  </si>
+  <si>
+    <t>新北市三重區仁愛街331號</t>
+  </si>
+  <si>
+    <t>三重溪美店</t>
+  </si>
+  <si>
+    <t>14:40:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>THILF04352</t>
+  </si>
+  <si>
+    <t>新北市三重區仁興街28巷44、46號</t>
+  </si>
+  <si>
+    <t>三重公園店</t>
+  </si>
+  <si>
     <t>12:20:00</t>
   </si>
   <si>
@@ -312,6 +378,21 @@
   </si>
   <si>
     <t>北縣溪尾二店</t>
+  </si>
+  <si>
+    <t>14:05:00</t>
+  </si>
+  <si>
+    <t>14:27:00</t>
+  </si>
+  <si>
+    <t>THILF0D620</t>
+  </si>
+  <si>
+    <t>新北市三重區仁愛街253號</t>
+  </si>
+  <si>
+    <t>三重福隆店</t>
   </si>
   <si>
     <t>吳宗鴻</t>
@@ -339,6 +420,27 @@
 送黑色碳粉 1</t>
   </si>
   <si>
+    <t>15:20:00</t>
+  </si>
+  <si>
+    <t>T252000153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">德森精密有限公司 </t>
+  </si>
+  <si>
+    <t>新北市林口區文化北路1段60巷108號3樓</t>
+  </si>
+  <si>
+    <t>有報修列印10分鐘才印出，測試筆電網速連線皆為正常</t>
+  </si>
+  <si>
+    <t>15:40:00</t>
+  </si>
+  <si>
+    <t>PM抄表</t>
+  </si>
+  <si>
     <t>12:11:00</t>
   </si>
   <si>
@@ -360,9 +462,6 @@
     <t>淡水</t>
   </si>
   <si>
-    <t>PM抄表</t>
-  </si>
-  <si>
     <t>11:00:00</t>
   </si>
   <si>
@@ -396,9 +495,6 @@
     <t>林口長庚分行</t>
   </si>
   <si>
-    <t>15:10:00</t>
-  </si>
-  <si>
     <t>T302800183</t>
   </si>
   <si>
@@ -456,12 +552,6 @@
     <t>林口文化1F營業部</t>
   </si>
   <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
     <t>THILF02596</t>
   </si>
   <si>
@@ -474,6 +564,23 @@
     <t>裝潢撤機完工</t>
   </si>
   <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>THILF05075</t>
+  </si>
+  <si>
+    <t>桃園市龜山區復興街185號1樓</t>
+  </si>
+  <si>
+    <t>龜山復興店</t>
+  </si>
+  <si>
+    <t>更換發票機
+換下8155003142
+換上8155005808</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
@@ -495,9 +602,6 @@
     <t>14:30:00</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
     <t>T252000102</t>
   </si>
   <si>
@@ -513,9 +617,6 @@
     <t>列印文字異常 更換PS3驅動</t>
   </si>
   <si>
-    <t>15:20:00</t>
-  </si>
-  <si>
     <t>T252000136</t>
   </si>
   <si>
@@ -645,10 +746,16 @@
     <t>節目部</t>
   </si>
   <si>
+    <t>T352500250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宏偉營造股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區光復路1段61巷26號2樓</t>
+  </si>
+  <si>
     <t>13:00:00</t>
-  </si>
-  <si>
-    <t>13:30:00</t>
   </si>
   <si>
     <t>T352800011</t>
@@ -1122,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB51"/>
+  <dimension ref="A1:AB61"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1278,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="7">
-        <v>2026090305</v>
+        <v>2026090520</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
@@ -1313,18 +1420,18 @@
       <c r="M3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="8"/>
+      <c r="O3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="7"/>
+      <c r="P3" s="7">
+        <v>6063</v>
+      </c>
       <c r="Q3" s="7">
-        <v>5118</v>
+        <v>12268</v>
       </c>
       <c r="R3" s="7">
-        <v>21005</v>
+        <v>37399</v>
       </c>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -1334,10 +1441,10 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB3" s="7">
         <v>1</v>
@@ -1348,7 +1455,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2026090043</v>
+        <v>2026090305</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -1360,7 +1467,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>43</v>
@@ -1372,33 +1479,31 @@
         <v>45</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3">
-        <v>4289</v>
+        <v>5118</v>
       </c>
       <c r="R4" s="3">
-        <v>3065</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>42</v>
-      </c>
+        <v>21005</v>
+      </c>
+      <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -1406,10 +1511,10 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB4" s="3">
         <v>1</v>
@@ -1420,7 +1525,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>2026090044</v>
+        <v>2026090043</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -1432,34 +1537,34 @@
         <v>30</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7">
@@ -1468,7 +1573,9 @@
       <c r="R5" s="7">
         <v>3065</v>
       </c>
-      <c r="S5" s="7"/>
+      <c r="S5" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -1476,19 +1583,21 @@
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="8" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB5" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="AB5" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:28">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2026090412</v>
+        <v>2026090044</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1500,25 +1609,25 @@
         <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>54</v>
@@ -1527,16 +1636,16 @@
         <v>55</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="Q6" s="3">
+        <v>4289</v>
+      </c>
       <c r="R6" s="3">
-        <v>85015</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>42</v>
-      </c>
+        <v>3065</v>
+      </c>
+      <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1544,21 +1653,19 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>1</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="AB6" s="3"/>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026090226</v>
+        <v>2026090412</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1570,10 +1677,10 @@
         <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>57</v>
@@ -1585,26 +1692,28 @@
         <v>59</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="N7" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="N7" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="O7" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7">
-        <v>0</v>
-      </c>
-      <c r="S7" s="7"/>
+        <v>85015</v>
+      </c>
+      <c r="S7" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -1612,10 +1721,10 @@
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="8" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB7" s="7">
         <v>1</v>
@@ -1626,7 +1735,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026090431</v>
+        <v>2026090226</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1638,21 +1747,25 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="L8" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>69</v>
@@ -1661,29 +1774,25 @@
         <v>70</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
-      <c r="Y8" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="Y8" s="3"/>
       <c r="Z8" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB8" s="3">
         <v>1</v>
@@ -1694,7 +1803,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026090332</v>
+        <v>2026090431</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1709,27 +1818,27 @@
         <v>31</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
@@ -1737,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
@@ -1745,13 +1854,13 @@
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
       <c r="Y9" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z9" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AA9" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB9" s="7">
         <v>1</v>
@@ -1762,7 +1871,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026090057</v>
+        <v>2026090332</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1774,61 +1883,63 @@
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>60</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
       <c r="L10" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
         <v>0</v>
       </c>
-      <c r="S10" s="3"/>
+      <c r="S10" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
+      <c r="Y10" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z10" s="6" t="s">
         <v>78</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB10" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:28">
       <c r="A11" s="7">
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026090053</v>
+        <v>2026090057</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1840,21 +1951,25 @@
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="J11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="L11" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>82</v>
@@ -1863,40 +1978,34 @@
         <v>83</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
         <v>0</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
-      <c r="Y11" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB11" s="7">
-        <v>1</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="AB11" s="7"/>
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026090205</v>
+        <v>2026090053</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1908,30 +2017,30 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -1939,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -1947,13 +2056,13 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB12" s="3">
         <v>1</v>
@@ -1964,7 +2073,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026090213</v>
+        <v>2026090205</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -1976,30 +2085,30 @@
         <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -2007,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
@@ -2015,13 +2124,13 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z13" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB13" s="7">
         <v>1</v>
@@ -2032,7 +2141,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026090242</v>
+        <v>2026090493</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2041,28 +2150,24 @@
         <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
       <c r="L14" s="6" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>99</v>
@@ -2071,38 +2176,40 @@
         <v>100</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P14" s="3"/>
-      <c r="Q14" s="3">
-        <v>3064</v>
-      </c>
+      <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>165868</v>
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T14" s="3"/>
-      <c r="U14" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
+      <c r="Y14" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z14" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
+        <v>78</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:28">
       <c r="A15" s="7">
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026090243</v>
+        <v>2026090468</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2111,64 +2218,66 @@
         <v>29</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P15" s="7"/>
-      <c r="Q15" s="7">
-        <v>3064</v>
-      </c>
+      <c r="Q15" s="7"/>
       <c r="R15" s="7">
-        <v>165868</v>
-      </c>
-      <c r="S15" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
+      <c r="Y15" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z15" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:28">
       <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026090459</v>
+        <v>2026090482</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2177,57 +2286,55 @@
         <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
       <c r="L16" s="6" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3">
-        <v>30655</v>
+        <v>0</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
+      <c r="Y16" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z16" s="6" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB16" s="3">
         <v>1</v>
@@ -2238,7 +2345,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026090460</v>
+        <v>2026090213</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2247,64 +2354,66 @@
         <v>29</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7">
-        <v>30655</v>
-      </c>
-      <c r="S17" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
+      <c r="Y17" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z17" s="8" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AA17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB17" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:28">
       <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026090453</v>
+        <v>2026090475</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2313,55 +2422,55 @@
         <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
       <c r="L18" s="6" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="N18" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>120</v>
+      </c>
       <c r="O18" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3">
-        <v>39400</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+      <c r="Y18" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z18" s="6" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB18" s="3">
         <v>1</v>
@@ -2372,7 +2481,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026090454</v>
+        <v>2026090242</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2381,54 +2490,60 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="N19" s="8"/>
+        <v>126</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>127</v>
+      </c>
       <c r="O19" s="7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
+      <c r="Q19" s="7">
+        <v>3064</v>
+      </c>
       <c r="R19" s="7">
-        <v>39400</v>
-      </c>
-      <c r="S19" s="7"/>
+        <v>165868</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
+      <c r="U19" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA19" s="7" t="s">
-        <v>42</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AA19" s="7"/>
       <c r="AB19" s="7"/>
     </row>
     <row r="20" spans="1:28">
@@ -2436,7 +2551,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026090286</v>
+        <v>2026090243</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2445,56 +2560,54 @@
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
+      <c r="Q20" s="3">
+        <v>3064</v>
+      </c>
       <c r="R20" s="3">
-        <v>145888</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>42</v>
-      </c>
+        <v>165868</v>
+      </c>
+      <c r="S20" s="3"/>
       <c r="T20" s="3"/>
-      <c r="U20" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="6" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
@@ -2504,7 +2617,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026090287</v>
+        <v>2026090498</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2513,42 +2626,42 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>120</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="N21" s="8"/>
       <c r="O21" s="7" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
+      <c r="Q21" s="7">
+        <v>667</v>
+      </c>
       <c r="R21" s="7">
-        <v>145888</v>
+        <v>29333</v>
       </c>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -2558,17 +2671,21 @@
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
+        <v>133</v>
+      </c>
+      <c r="AA21" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB21" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:28">
       <c r="A22" s="3">
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026090284</v>
+        <v>2026090496</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2577,58 +2694,58 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>120</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="N22" s="6"/>
       <c r="O22" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
+      <c r="Q22" s="3">
+        <v>667</v>
+      </c>
       <c r="R22" s="3">
-        <v>11283</v>
+        <v>29333</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T22" s="3"/>
-      <c r="U22" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA22" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB22" s="3"/>
     </row>
     <row r="23" spans="1:28">
@@ -2636,7 +2753,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026090285</v>
+        <v>2026090497</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2645,42 +2762,42 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="N23" s="8" t="s">
-        <v>120</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
+      <c r="Q23" s="7">
+        <v>667</v>
+      </c>
       <c r="R23" s="7">
-        <v>11283</v>
+        <v>29333</v>
       </c>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -2690,9 +2807,11 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA23" s="7"/>
+        <v>135</v>
+      </c>
+      <c r="AA23" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB23" s="7"/>
     </row>
     <row r="24" spans="1:28">
@@ -2700,7 +2819,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026090457</v>
+        <v>2026090459</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2709,47 +2828,45 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3">
-        <v>3170</v>
-      </c>
+      <c r="Q24" s="3"/>
       <c r="R24" s="3">
-        <v>425348</v>
+        <v>30655</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -2758,10 +2875,10 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB24" s="3">
         <v>1</v>
@@ -2772,7 +2889,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026090458</v>
+        <v>2026090460</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2781,44 +2898,42 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P25" s="7"/>
-      <c r="Q25" s="7">
-        <v>3170</v>
-      </c>
+      <c r="Q25" s="7"/>
       <c r="R25" s="7">
-        <v>425348</v>
+        <v>30655</v>
       </c>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -2828,10 +2943,10 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="AA25" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB25" s="7"/>
     </row>
@@ -2840,7 +2955,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026090051</v>
+        <v>2026090453</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2849,47 +2964,43 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>135</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N26" s="6"/>
       <c r="O26" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3">
-        <v>121</v>
-      </c>
+      <c r="Q26" s="3"/>
       <c r="R26" s="3">
-        <v>191</v>
+        <v>39400</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -2898,10 +3009,10 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB26" s="3">
         <v>1</v>
@@ -2912,7 +3023,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026090052</v>
+        <v>2026090454</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -2921,44 +3032,40 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>135</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N27" s="8"/>
       <c r="O27" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P27" s="7"/>
-      <c r="Q27" s="7">
-        <v>121</v>
-      </c>
+      <c r="Q27" s="7"/>
       <c r="R27" s="7">
-        <v>191</v>
+        <v>39400</v>
       </c>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -2968,10 +3075,10 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="AA27" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB27" s="7"/>
     </row>
@@ -2980,7 +3087,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026090244</v>
+        <v>2026090286</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -2989,56 +3096,56 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3">
-        <v>270931</v>
+        <v>145888</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
@@ -3048,7 +3155,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026090245</v>
+        <v>2026090287</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3057,42 +3164,42 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7">
-        <v>270931</v>
+        <v>145888</v>
       </c>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
@@ -3102,7 +3209,7 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="AA29" s="7"/>
       <c r="AB29" s="7"/>
@@ -3112,7 +3219,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026090208</v>
+        <v>2026090284</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3121,64 +3228,66 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
+        <v>154</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L30" s="6" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3">
-        <v>0</v>
-      </c>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="U30" s="3"/>
+        <v>11283</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB30" s="3">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="1:28">
       <c r="A31" s="7">
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026090309</v>
+        <v>2026090285</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3187,42 +3296,44 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>148</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L31" s="8" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O31" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>0</v>
-      </c>
-      <c r="S31" s="7" t="s">
-        <v>42</v>
-      </c>
+        <v>11283</v>
+      </c>
+      <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -3230,21 +3341,17 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA31" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB31" s="7">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AA31" s="7"/>
+      <c r="AB31" s="7"/>
     </row>
     <row r="32" spans="1:28">
       <c r="A32" s="3">
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026090240</v>
+        <v>2026090457</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3253,46 +3360,48 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3">
-        <v>1900</v>
+        <v>3170</v>
       </c>
       <c r="R32" s="3">
-        <v>28500</v>
-      </c>
-      <c r="S32" s="3"/>
+        <v>425348</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3300,10 +3409,10 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="AA32" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB32" s="3">
         <v>1</v>
@@ -3314,7 +3423,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026090256</v>
+        <v>2026090458</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3323,44 +3432,44 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>37</v>
+        <v>159</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P33" s="7"/>
       <c r="Q33" s="7">
-        <v>6432</v>
+        <v>3170</v>
       </c>
       <c r="R33" s="7">
-        <v>770</v>
+        <v>425348</v>
       </c>
       <c r="S33" s="7"/>
       <c r="T33" s="7"/>
@@ -3370,21 +3479,19 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="AA33" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB33" s="7">
-        <v>1</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
       <c r="A34" s="3">
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026090405</v>
+        <v>2026090052</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3393,44 +3500,44 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3">
-        <v>770</v>
+        <v>121</v>
       </c>
       <c r="R34" s="3">
-        <v>6432</v>
+        <v>191</v>
       </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
@@ -3440,10 +3547,10 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="AA34" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB34" s="3">
         <v>1</v>
@@ -3454,7 +3561,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026090071</v>
+        <v>2026090051</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3463,44 +3570,48 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G35" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="H35" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>167</v>
-      </c>
       <c r="J35" s="7" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
+      <c r="Q35" s="7">
+        <v>121</v>
+      </c>
       <c r="R35" s="7">
-        <v>3953</v>
-      </c>
-      <c r="S35" s="7"/>
+        <v>191</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
       <c r="V35" s="7"/>
@@ -3508,21 +3619,19 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="AA35" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB35" s="7">
-        <v>1</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
       <c r="A36" s="3">
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026090075</v>
+        <v>2026090244</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3531,66 +3640,66 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3">
-        <v>11827</v>
-      </c>
-      <c r="S36" s="3"/>
+        <v>270931</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
+      <c r="U36" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB36" s="3">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28">
       <c r="A37" s="7">
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026090077</v>
+        <v>2026090245</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3599,42 +3708,42 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7">
-        <v>49123</v>
+        <v>270931</v>
       </c>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
@@ -3644,21 +3753,17 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA37" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB37" s="7">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
     </row>
     <row r="38" spans="1:28">
       <c r="A38" s="3">
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026090074</v>
+        <v>2026090208</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3667,55 +3772,53 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
       <c r="L38" s="6" t="s">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3">
-        <v>61971</v>
+        <v>0</v>
       </c>
       <c r="S38" s="3"/>
-      <c r="T38" s="3"/>
+      <c r="T38" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>41</v>
+        <v>176</v>
       </c>
       <c r="AA38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB38" s="3">
         <v>1</v>
@@ -3726,7 +3829,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026090079</v>
+        <v>2026090392</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -3735,42 +3838,42 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
       <c r="R39" s="7">
-        <v>39446</v>
+        <v>0</v>
       </c>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
@@ -3780,10 +3883,10 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
       <c r="AA39" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB39" s="7">
         <v>1</v>
@@ -3794,7 +3897,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026090073</v>
+        <v>2026090309</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -3803,44 +3906,42 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="N40" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>189</v>
-      </c>
       <c r="O40" s="3" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3">
-        <v>45148</v>
-      </c>
-      <c r="S40" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
@@ -3848,10 +3949,10 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="AA40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB40" s="3">
         <v>1</v>
@@ -3862,7 +3963,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026090072</v>
+        <v>2026090240</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -3871,28 +3972,28 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="M41" s="8" t="s">
         <v>191</v>
@@ -3901,12 +4002,14 @@
         <v>192</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="P41" s="7"/>
-      <c r="Q41" s="7"/>
+      <c r="Q41" s="7">
+        <v>1900</v>
+      </c>
       <c r="R41" s="7">
-        <v>23897</v>
+        <v>28500</v>
       </c>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
@@ -3916,10 +4019,10 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="AA41" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB41" s="7">
         <v>1</v>
@@ -3930,7 +4033,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026090406</v>
+        <v>2026090256</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -3939,42 +4042,44 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L42" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M42" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="M42" s="6" t="s">
-        <v>196</v>
-      </c>
       <c r="N42" s="6" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
+      <c r="Q42" s="3">
+        <v>6432</v>
+      </c>
       <c r="R42" s="3">
-        <v>124253</v>
+        <v>770</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
@@ -3984,10 +4089,10 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="AA42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB42" s="3">
         <v>1</v>
@@ -3998,7 +4103,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026090078</v>
+        <v>2026090405</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4007,42 +4112,44 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>168</v>
+        <v>47</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P43" s="7"/>
-      <c r="Q43" s="7"/>
+      <c r="Q43" s="7">
+        <v>770</v>
+      </c>
       <c r="R43" s="7">
-        <v>1150</v>
+        <v>6432</v>
       </c>
       <c r="S43" s="7"/>
       <c r="T43" s="7"/>
@@ -4052,10 +4159,10 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>41</v>
+        <v>198</v>
       </c>
       <c r="AA43" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB43" s="7">
         <v>1</v>
@@ -4066,7 +4173,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026090076</v>
+        <v>2026090071</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4075,28 +4182,28 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>66</v>
+        <v>199</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>202</v>
@@ -4105,12 +4212,12 @@
         <v>203</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>6813</v>
+        <v>3953</v>
       </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
@@ -4120,10 +4227,10 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="AA44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB44" s="3">
         <v>1</v>
@@ -4134,7 +4241,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026090465</v>
+        <v>2026090075</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4143,42 +4250,42 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G45" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="I45" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="I45" s="7" t="s">
-        <v>206</v>
-      </c>
       <c r="J45" s="7" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7">
-        <v>53932</v>
+        <v>11827</v>
       </c>
       <c r="S45" s="7"/>
       <c r="T45" s="7"/>
@@ -4188,10 +4295,10 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="AA45" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB45" s="7">
         <v>1</v>
@@ -4202,7 +4309,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026090432</v>
+        <v>2026090077</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4211,42 +4318,42 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3">
-        <v>30234</v>
+        <v>49123</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
@@ -4256,10 +4363,10 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="AA46" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB46" s="3">
         <v>1</v>
@@ -4270,7 +4377,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026090428</v>
+        <v>2026090074</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4279,42 +4386,42 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
       <c r="R47" s="7">
-        <v>130586</v>
+        <v>61971</v>
       </c>
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
@@ -4324,10 +4431,10 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="AA47" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB47" s="7">
         <v>1</v>
@@ -4338,7 +4445,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026090407</v>
+        <v>2026090079</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4347,42 +4454,42 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>214</v>
+        <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3">
-        <v>280656</v>
+        <v>39446</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
@@ -4392,10 +4499,10 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="AA48" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB48" s="3">
         <v>1</v>
@@ -4406,7 +4513,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026090430</v>
+        <v>2026090073</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4415,42 +4522,42 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>66</v>
+        <v>219</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="M49" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="N49" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="N49" s="8" t="s">
-        <v>223</v>
-      </c>
       <c r="O49" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P49" s="7"/>
       <c r="Q49" s="7"/>
       <c r="R49" s="7">
-        <v>212550</v>
+        <v>45148</v>
       </c>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
@@ -4460,10 +4567,10 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>165</v>
+        <v>50</v>
       </c>
       <c r="AA49" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB49" s="7">
         <v>1</v>
@@ -4474,7 +4581,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026090466</v>
+        <v>2026090072</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4483,42 +4590,42 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>142</v>
+        <v>219</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3">
-        <v>212550</v>
+        <v>23897</v>
       </c>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
@@ -4528,47 +4635,729 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="AA50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:28">
+      <c r="A51" s="7">
+        <v>49</v>
+      </c>
+      <c r="B51" s="7">
+        <v>2026090406</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="O51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7">
+        <v>124253</v>
+      </c>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="7"/>
+      <c r="W51" s="7"/>
+      <c r="X51" s="7"/>
+      <c r="Y51" s="7"/>
+      <c r="Z51" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB51" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:28">
+      <c r="A52" s="3">
+        <v>50</v>
+      </c>
+      <c r="B52" s="3">
+        <v>2026090078</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AB50" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="10"/>
-      <c r="AA51" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="AB51" s="9">
-        <v>34</v>
+      <c r="G52" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3">
+        <v>1150</v>
+      </c>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:28">
+      <c r="A53" s="7">
+        <v>51</v>
+      </c>
+      <c r="B53" s="7">
+        <v>2026090076</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="N53" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="O53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7">
+        <v>6813</v>
+      </c>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
+      <c r="Y53" s="7"/>
+      <c r="Z53" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA53" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB53" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28">
+      <c r="A54" s="3">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3">
+        <v>2026090477</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3">
+        <v>2506</v>
+      </c>
+      <c r="R54" s="3">
+        <v>6417</v>
+      </c>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:28">
+      <c r="A55" s="7">
+        <v>53</v>
+      </c>
+      <c r="B55" s="7">
+        <v>2026090465</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7">
+        <v>53932</v>
+      </c>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB55" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:28">
+      <c r="A56" s="3">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3">
+        <v>2026090432</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3">
+        <v>30234</v>
+      </c>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:28">
+      <c r="A57" s="7">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7">
+        <v>2026090428</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="N57" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7">
+        <v>130586</v>
+      </c>
+      <c r="S57" s="7"/>
+      <c r="T57" s="7"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
+      <c r="Y57" s="7"/>
+      <c r="Z57" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA57" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB57" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:28">
+      <c r="A58" s="3">
+        <v>56</v>
+      </c>
+      <c r="B58" s="3">
+        <v>2026090407</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3">
+        <v>280656</v>
+      </c>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:28">
+      <c r="A59" s="7">
+        <v>57</v>
+      </c>
+      <c r="B59" s="7">
+        <v>2026090430</v>
+      </c>
+      <c r="C59" s="7">
+        <v>1</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="O59" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7">
+        <v>212550</v>
+      </c>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
+      <c r="U59" s="7"/>
+      <c r="V59" s="7"/>
+      <c r="W59" s="7"/>
+      <c r="X59" s="7"/>
+      <c r="Y59" s="7"/>
+      <c r="Z59" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA59" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB59" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:28">
+      <c r="A60" s="3">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3">
+        <v>2026090466</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3">
+        <v>212550</v>
+      </c>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28">
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9"/>
+      <c r="R61" s="9"/>
+      <c r="S61" s="9"/>
+      <c r="T61" s="9"/>
+      <c r="U61" s="9"/>
+      <c r="V61" s="9"/>
+      <c r="W61" s="9"/>
+      <c r="X61" s="9"/>
+      <c r="Y61" s="9"/>
+      <c r="Z61" s="10"/>
+      <c r="AA61" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AB61" s="9">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202609_Service_Count_Report.xlsx
+++ b/IM/202609_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$81</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="329">
   <si>
     <t>服務次數統計表        篩選月份：202609</t>
   </si>
@@ -221,6 +221,42 @@
     <t>天玉街</t>
   </si>
   <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>09:53:00</t>
+  </si>
+  <si>
+    <t>T302800122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">虹揚印刷股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區橋和路120號6樓</t>
+  </si>
+  <si>
+    <t>6F</t>
+  </si>
+  <si>
+    <t>碳粉28趴</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>T302800181</t>
+  </si>
+  <si>
+    <t>新北市中和區橋和路120號9樓之7</t>
+  </si>
+  <si>
+    <t>9F</t>
+  </si>
+  <si>
+    <t>碳粉要備用</t>
+  </si>
+  <si>
     <t>12:50:00</t>
   </si>
   <si>
@@ -365,6 +401,24 @@
     <t>三重公園店</t>
   </si>
   <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>THILF0C660</t>
+  </si>
+  <si>
+    <t>新北市中和區中和路414號</t>
+  </si>
+  <si>
+    <t>中和永安市場</t>
+  </si>
+  <si>
+    <t>換上8185002267 換下8185000572</t>
+  </si>
+  <si>
     <t>12:20:00</t>
   </si>
   <si>
@@ -398,7 +452,19 @@
     <t>吳宗鴻</t>
   </si>
   <si>
-    <t>14:00:00</t>
+    <t>10:10:00</t>
+  </si>
+  <si>
+    <t>T252000025</t>
+  </si>
+  <si>
+    <t>新北市泰山區莊田路與信華三街交叉口(華固一莊)</t>
+  </si>
+  <si>
+    <t>華固一莊</t>
+  </si>
+  <si>
+    <t>PM抄表</t>
   </si>
   <si>
     <t>14:25:00</t>
@@ -438,9 +504,6 @@
     <t>15:40:00</t>
   </si>
   <si>
-    <t>PM抄表</t>
-  </si>
-  <si>
     <t>12:11:00</t>
   </si>
   <si>
@@ -495,6 +558,21 @@
     <t>林口長庚分行</t>
   </si>
   <si>
+    <t>11:45:00</t>
+  </si>
+  <si>
+    <t>T302800143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台灣大哥大股份有限公司 </t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區南工路1段18號(工務倉庫)</t>
+  </si>
+  <si>
+    <t>桃園工務倉庫(黑)</t>
+  </si>
+  <si>
     <t>T302800183</t>
   </si>
   <si>
@@ -564,7 +642,43 @@
     <t>裝潢撤機完工</t>
   </si>
   <si>
+    <t>THILF02620</t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區南崁路一段336號B1</t>
+  </si>
+  <si>
+    <t>桃縣桃科店</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>12:10:00</t>
+  </si>
+  <si>
+    <t>THILF02988</t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區南工路150號</t>
+  </si>
+  <si>
+    <t>蘆竹蘆興店</t>
+  </si>
+  <si>
+    <t>13:10:00</t>
+  </si>
+  <si>
     <t>13:30:00</t>
+  </si>
+  <si>
+    <t>THILF04601</t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區南崁路一段286號</t>
+  </si>
+  <si>
+    <t>蘆竹領航星</t>
   </si>
   <si>
     <t>THILF05075</t>
@@ -632,6 +746,15 @@
     <t>pm</t>
   </si>
   <si>
+    <t>T301800009</t>
+  </si>
+  <si>
+    <t>新北市三重區重新路五段609巷2號3樓-3</t>
+  </si>
+  <si>
+    <t>台北客服3樓-3</t>
+  </si>
+  <si>
     <t>08:50:00</t>
   </si>
   <si>
@@ -647,7 +770,25 @@
     <t>異地備援泰山</t>
   </si>
   <si>
-    <t>10:10:00</t>
+    <t>T301800078</t>
+  </si>
+  <si>
+    <t>新北市五股區五權路48號2樓(五股倉庫)</t>
+  </si>
+  <si>
+    <t>五股倉庫(黑)</t>
+  </si>
+  <si>
+    <t>09:10:00</t>
+  </si>
+  <si>
+    <t>T302800029</t>
+  </si>
+  <si>
+    <t>新北市三重區重新路5段609巷2號3樓</t>
+  </si>
+  <si>
+    <t>三重湯城4樓(黑)J22</t>
   </si>
   <si>
     <t>T302800053</t>
@@ -671,9 +812,6 @@
     <t>營管部</t>
   </si>
   <si>
-    <t>09:30:00</t>
-  </si>
-  <si>
     <t>T302800153</t>
   </si>
   <si>
@@ -692,9 +830,6 @@
     <t>櫃台2</t>
   </si>
   <si>
-    <t>09:10:00</t>
-  </si>
-  <si>
     <t>T302800155</t>
   </si>
   <si>
@@ -713,6 +848,15 @@
     <t>工程部1</t>
   </si>
   <si>
+    <t>T351500177</t>
+  </si>
+  <si>
+    <t>新北市三重區重新路五段609巷2號4樓-2(客服)</t>
+  </si>
+  <si>
+    <t>台北客服4樓2LJ12銷支科(彩)</t>
+  </si>
+  <si>
     <t>T351800045</t>
   </si>
   <si>
@@ -755,9 +899,6 @@
     <t>新北市三重區光復路1段61巷26號2樓</t>
   </si>
   <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
     <t>T352800011</t>
   </si>
   <si>
@@ -813,6 +954,69 @@
   </si>
   <si>
     <t>卡紙更換取送分x4</t>
+  </si>
+  <si>
+    <t>T452800007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東森電視事業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區重新路5段609巷10號9樓</t>
+  </si>
+  <si>
+    <t>三重湯城</t>
+  </si>
+  <si>
+    <t>送碳粉 更換OD OD刮回刮 上熱</t>
+  </si>
+  <si>
+    <t>T452800031</t>
+  </si>
+  <si>
+    <t>新北市三重區重新路五段609巷2號4樓-2(三重湯城)</t>
+  </si>
+  <si>
+    <t>台北客服4樓-2LJ23(黑)</t>
+  </si>
+  <si>
+    <t>T452800032</t>
+  </si>
+  <si>
+    <t>台北客服4樓-2LJ15(黑)</t>
+  </si>
+  <si>
+    <t>狄澤洋</t>
+  </si>
+  <si>
+    <t>12:35:00</t>
+  </si>
+  <si>
+    <t>THILF0D111</t>
+  </si>
+  <si>
+    <t>新北市板橋區府中路24號</t>
+  </si>
+  <si>
+    <t>板橋府中店</t>
+  </si>
+  <si>
+    <t>螢幕清潔線路重新插拔，觀察一段時間測試正常</t>
+  </si>
+  <si>
+    <t>12:15:00</t>
+  </si>
+  <si>
+    <t>12:29:00</t>
+  </si>
+  <si>
+    <t>THILF0L501</t>
+  </si>
+  <si>
+    <t>新北市板橋區中山路一段279號</t>
+  </si>
+  <si>
+    <t>車麗屋板橋店</t>
   </si>
   <si>
     <t>合計</t>
@@ -1229,7 +1433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB61"/>
+  <dimension ref="A1:AB81"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1735,7 +1939,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026090226</v>
+        <v>2026090602</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1747,39 +1951,39 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="J8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="M8" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="N8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="O8" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>42846</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1789,7 +1993,7 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>41</v>
@@ -1803,7 +2007,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026090431</v>
+        <v>2026090599</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -1815,49 +2019,49 @@
         <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="N9" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="N9" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="O9" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7">
-        <v>0</v>
-      </c>
-      <c r="S9" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>17803</v>
+      </c>
+      <c r="S9" s="7"/>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
-      <c r="Y9" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y9" s="7"/>
       <c r="Z9" s="8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="AA9" s="7" t="s">
         <v>41</v>
@@ -1871,7 +2075,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026090332</v>
+        <v>2026090226</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1883,49 +2087,49 @@
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="L10" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="M10" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M10" s="6" t="s">
+      <c r="N10" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="O10" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
         <v>0</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
-      <c r="Y10" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y10" s="3"/>
       <c r="Z10" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>41</v>
@@ -1939,7 +2143,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026090057</v>
+        <v>2026090431</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -1951,61 +2155,63 @@
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G11" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="M11" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
         <v>0</v>
       </c>
-      <c r="S11" s="7"/>
+      <c r="S11" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
+      <c r="Y11" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z11" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB11" s="7"/>
+      <c r="AB11" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:28">
       <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026090053</v>
+        <v>2026090332</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -2020,24 +2226,24 @@
         <v>42</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>56</v>
@@ -2059,7 +2265,7 @@
         <v>41</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>41</v>
@@ -2073,7 +2279,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026090205</v>
+        <v>2026090057</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -2088,18 +2294,22 @@
         <v>42</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="J13" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="L13" s="8" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M13" s="8" t="s">
         <v>94</v>
@@ -2108,40 +2318,34 @@
         <v>95</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
         <v>0</v>
       </c>
-      <c r="S13" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="S13" s="7"/>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB13" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB13" s="7"/>
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026090493</v>
+        <v>2026090053</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2153,27 +2357,27 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>56</v>
@@ -2195,7 +2399,7 @@
         <v>41</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>41</v>
@@ -2209,7 +2413,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026090468</v>
+        <v>2026090205</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2221,27 +2425,27 @@
         <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>56</v>
@@ -2263,7 +2467,7 @@
         <v>41</v>
       </c>
       <c r="Z15" s="8" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>41</v>
@@ -2277,7 +2481,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026090482</v>
+        <v>2026090493</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2292,24 +2496,24 @@
         <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>56</v>
@@ -2331,7 +2535,7 @@
         <v>41</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>41</v>
@@ -2345,7 +2549,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026090213</v>
+        <v>2026090468</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2357,27 +2561,27 @@
         <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="8" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>56</v>
@@ -2399,7 +2603,7 @@
         <v>41</v>
       </c>
       <c r="Z17" s="8" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>41</v>
@@ -2413,7 +2617,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026090475</v>
+        <v>2026090482</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2428,24 +2632,24 @@
         <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>56</v>
@@ -2467,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>41</v>
@@ -2481,7 +2685,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026090242</v>
+        <v>2026090584</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2490,28 +2694,28 @@
         <v>29</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="M19" s="8" t="s">
         <v>126</v>
@@ -2520,22 +2724,16 @@
         <v>127</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="P19" s="7"/>
-      <c r="Q19" s="7">
-        <v>3064</v>
-      </c>
+      <c r="Q19" s="7"/>
       <c r="R19" s="7">
-        <v>165868</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S19" s="7"/>
       <c r="T19" s="7"/>
-      <c r="U19" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U19" s="7"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
@@ -2543,15 +2741,19 @@
       <c r="Z19" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
+      <c r="AA19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:28">
       <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026090243</v>
+        <v>2026090213</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2560,64 +2762,66 @@
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
       <c r="L20" s="6" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3">
-        <v>3064</v>
-      </c>
+      <c r="Q20" s="3"/>
       <c r="R20" s="3">
-        <v>165868</v>
-      </c>
-      <c r="S20" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
+      <c r="Y20" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z20" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA20" s="3"/>
-      <c r="AB20" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:28">
       <c r="A21" s="7">
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026090498</v>
+        <v>2026090475</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2626,52 +2830,52 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
       <c r="L21" s="8" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="N21" s="8"/>
+        <v>137</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="O21" s="7" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="P21" s="7"/>
-      <c r="Q21" s="7">
-        <v>667</v>
-      </c>
+      <c r="Q21" s="7"/>
       <c r="R21" s="7">
-        <v>29333</v>
-      </c>
-      <c r="S21" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
+      <c r="Y21" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z21" s="8" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>41</v>
@@ -2685,7 +2889,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026090496</v>
+        <v>2026090613</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2694,19 +2898,19 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>46</v>
@@ -2715,21 +2919,25 @@
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="N22" s="6"/>
+        <v>142</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>143</v>
+      </c>
       <c r="O22" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="P22" s="3"/>
+      <c r="P22" s="3">
+        <v>8173</v>
+      </c>
       <c r="Q22" s="3">
-        <v>667</v>
+        <v>18275</v>
       </c>
       <c r="R22" s="3">
-        <v>29333</v>
+        <v>26694</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>41</v>
@@ -2741,19 +2949,21 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="6" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB22" s="3"/>
+      <c r="AB22" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026090497</v>
+        <v>2026090614</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2762,19 +2972,19 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>46</v>
@@ -2783,21 +2993,25 @@
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>131</v>
+        <v>37</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="N23" s="8"/>
+        <v>142</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>143</v>
+      </c>
       <c r="O23" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P23" s="7"/>
+      <c r="P23" s="7">
+        <v>8173</v>
+      </c>
       <c r="Q23" s="7">
-        <v>667</v>
+        <v>18275</v>
       </c>
       <c r="R23" s="7">
-        <v>29333</v>
+        <v>26694</v>
       </c>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -2807,7 +3021,7 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
       <c r="Z23" s="8" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="AA23" s="7" t="s">
         <v>41</v>
@@ -2819,7 +3033,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026090459</v>
+        <v>2026090242</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -2828,68 +3042,68 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>56</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
+      <c r="Q24" s="3">
+        <v>3064</v>
+      </c>
       <c r="R24" s="3">
-        <v>30655</v>
+        <v>165868</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
+      <c r="U24" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026090460</v>
+        <v>2026090243</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -2898,42 +3112,44 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>139</v>
+        <v>46</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="O25" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="Q25" s="7">
+        <v>3064</v>
+      </c>
       <c r="R25" s="7">
-        <v>30655</v>
+        <v>165868</v>
       </c>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -2943,11 +3159,9 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA25" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
     </row>
     <row r="26" spans="1:28">
@@ -2955,7 +3169,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026090453</v>
+        <v>2026090498</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -2964,44 +3178,44 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
+      <c r="Q26" s="3">
+        <v>667</v>
+      </c>
       <c r="R26" s="3">
-        <v>39400</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>29333</v>
+      </c>
+      <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -3009,7 +3223,7 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>41</v>
@@ -3023,7 +3237,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026090454</v>
+        <v>2026090496</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -3032,42 +3246,46 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="N27" s="8"/>
       <c r="O27" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
+      <c r="Q27" s="7">
+        <v>667</v>
+      </c>
       <c r="R27" s="7">
-        <v>39400</v>
-      </c>
-      <c r="S27" s="7"/>
+        <v>29333</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
@@ -3075,7 +3293,7 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="AA27" s="7" t="s">
         <v>41</v>
@@ -3087,7 +3305,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026090286</v>
+        <v>2026090497</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -3096,58 +3314,56 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>153</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N28" s="6"/>
       <c r="O28" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
+      <c r="Q28" s="3">
+        <v>667</v>
+      </c>
       <c r="R28" s="3">
-        <v>145888</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>29333</v>
+      </c>
+      <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA28" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="AA28" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB28" s="3"/>
     </row>
     <row r="29" spans="1:28">
@@ -3155,7 +3371,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026090287</v>
+        <v>2026090459</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3164,44 +3380,46 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7">
-        <v>145888</v>
-      </c>
-      <c r="S29" s="7"/>
+        <v>30655</v>
+      </c>
+      <c r="S29" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
@@ -3209,17 +3427,21 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA29" s="7"/>
-      <c r="AB29" s="7"/>
+        <v>144</v>
+      </c>
+      <c r="AA29" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB29" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026090284</v>
+        <v>2026090460</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3228,58 +3450,56 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3">
-        <v>11283</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>30655</v>
+      </c>
+      <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA30" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="AA30" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB30" s="3"/>
     </row>
     <row r="31" spans="1:28">
@@ -3287,7 +3507,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026090285</v>
+        <v>2026090453</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3296,19 +3516,19 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>59</v>
@@ -3317,23 +3537,23 @@
         <v>36</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>153</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N31" s="8"/>
       <c r="O31" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>11283</v>
-      </c>
-      <c r="S31" s="7"/>
+        <v>39400</v>
+      </c>
+      <c r="S31" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -3341,17 +3561,21 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA31" s="7"/>
-      <c r="AB31" s="7"/>
+        <v>144</v>
+      </c>
+      <c r="AA31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB31" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:28">
       <c r="A32" s="3">
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026090457</v>
+        <v>2026090454</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3360,48 +3584,42 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>142</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N32" s="6"/>
       <c r="O32" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P32" s="3"/>
-      <c r="Q32" s="3">
-        <v>3170</v>
-      </c>
+      <c r="Q32" s="3"/>
       <c r="R32" s="3">
-        <v>425348</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>39400</v>
+      </c>
+      <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3409,21 +3627,19 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB32" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB32" s="3"/>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026090458</v>
+        <v>2026090286</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3432,58 +3648,58 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>158</v>
+        <v>59</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P33" s="7"/>
-      <c r="Q33" s="7">
-        <v>3170</v>
-      </c>
+      <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>425348</v>
-      </c>
-      <c r="S33" s="7"/>
+        <v>145888</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
+      <c r="U33" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA33" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
     </row>
     <row r="34" spans="1:28">
@@ -3491,7 +3707,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026090052</v>
+        <v>2026090287</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3500,44 +3716,42 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P34" s="3"/>
-      <c r="Q34" s="3">
-        <v>121</v>
-      </c>
+      <c r="Q34" s="3"/>
       <c r="R34" s="3">
-        <v>191</v>
+        <v>145888</v>
       </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
@@ -3547,21 +3761,17 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB34" s="3">
-        <v>1</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
     </row>
     <row r="35" spans="1:28">
       <c r="A35" s="7">
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026090051</v>
+        <v>2026090628</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3570,44 +3780,42 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>161</v>
+        <v>32</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="O35" s="7" t="s">
         <v>56</v>
       </c>
       <c r="P35" s="7"/>
-      <c r="Q35" s="7">
-        <v>121</v>
-      </c>
+      <c r="Q35" s="7"/>
       <c r="R35" s="7">
-        <v>191</v>
+        <v>12306</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>41</v>
@@ -3619,11 +3827,9 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA35" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="AA35" s="7"/>
       <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
@@ -3631,7 +3837,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026090244</v>
+        <v>2026090629</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3640,58 +3846,56 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3">
-        <v>270931</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>12306</v>
+      </c>
+      <c r="S36" s="3"/>
       <c r="T36" s="3"/>
-      <c r="U36" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA36" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28">
@@ -3699,7 +3903,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026090245</v>
+        <v>2026090284</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3708,52 +3912,56 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7">
-        <v>270931</v>
-      </c>
-      <c r="S37" s="7"/>
+        <v>11283</v>
+      </c>
+      <c r="S37" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
+      <c r="U37" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="AA37" s="7"/>
       <c r="AB37" s="7"/>
@@ -3763,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026090208</v>
+        <v>2026090285</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3772,64 +3980,62 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="I38" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="M38" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M38" s="6" t="s">
+      <c r="N38" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="N38" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="O38" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3">
-        <v>0</v>
+        <v>11283</v>
       </c>
       <c r="S38" s="3"/>
-      <c r="T38" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB38" s="3">
-        <v>1</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
     </row>
     <row r="39" spans="1:28">
       <c r="A39" s="7">
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026090392</v>
+        <v>2026090457</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -3838,44 +4044,48 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>66</v>
+        <v>184</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="N39" s="8" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
+      <c r="Q39" s="7">
+        <v>3170</v>
+      </c>
       <c r="R39" s="7">
-        <v>0</v>
-      </c>
-      <c r="S39" s="7"/>
+        <v>425348</v>
+      </c>
+      <c r="S39" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
@@ -3883,7 +4093,7 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="AA39" s="7" t="s">
         <v>41</v>
@@ -3897,7 +4107,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026090309</v>
+        <v>2026090458</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -3906,42 +4116,46 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="I40" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L40" s="6" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
+      <c r="Q40" s="3">
+        <v>3170</v>
+      </c>
       <c r="R40" s="3">
-        <v>0</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>425348</v>
+      </c>
+      <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
@@ -3949,21 +4163,19 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AA40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB40" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB40" s="3"/>
     </row>
     <row r="41" spans="1:28">
       <c r="A41" s="7">
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026090240</v>
+        <v>2026090051</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -3972,46 +4184,48 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G41" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="H41" s="7" t="s">
         <v>188</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>107</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>189</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7">
-        <v>1900</v>
+        <v>121</v>
       </c>
       <c r="R41" s="7">
-        <v>28500</v>
-      </c>
-      <c r="S41" s="7"/>
+        <v>191</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
@@ -4019,7 +4233,7 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="AA41" s="7" t="s">
         <v>41</v>
@@ -4033,7 +4247,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026090256</v>
+        <v>2026090052</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4042,44 +4256,44 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>47</v>
+        <v>191</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3">
-        <v>6432</v>
+        <v>121</v>
       </c>
       <c r="R42" s="3">
-        <v>770</v>
+        <v>191</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
@@ -4089,21 +4303,19 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB42" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB42" s="3"/>
     </row>
     <row r="43" spans="1:28">
       <c r="A43" s="7">
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026090405</v>
+        <v>2026090244</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4112,68 +4324,66 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G43" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="J43" s="7" t="s">
         <v>196</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P43" s="7"/>
-      <c r="Q43" s="7">
-        <v>770</v>
-      </c>
+      <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>6432</v>
-      </c>
-      <c r="S43" s="7"/>
+        <v>270931</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
+      <c r="U43" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA43" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB43" s="7">
-        <v>1</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AA43" s="7"/>
+      <c r="AB43" s="7"/>
     </row>
     <row r="44" spans="1:28">
       <c r="A44" s="3">
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026090071</v>
+        <v>2026090245</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4182,34 +4392,34 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G44" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J44" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>201</v>
+        <v>147</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>39</v>
@@ -4217,7 +4427,7 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>3953</v>
+        <v>270931</v>
       </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
@@ -4227,21 +4437,17 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA44" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>1</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="AA44" s="3"/>
+      <c r="AB44" s="3"/>
     </row>
     <row r="45" spans="1:28">
       <c r="A45" s="7">
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026090075</v>
+        <v>2026090208</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4250,52 +4456,50 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>204</v>
+        <v>33</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
       <c r="L45" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="N45" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="M45" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="N45" s="8" t="s">
-        <v>207</v>
-      </c>
       <c r="O45" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7">
-        <v>11827</v>
+        <v>0</v>
       </c>
       <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
+      <c r="T45" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
       <c r="W45" s="7"/>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="AA45" s="7" t="s">
         <v>41</v>
@@ -4309,7 +4513,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026090077</v>
+        <v>2026090656</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4318,44 +4522,42 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>208</v>
+        <v>124</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
       <c r="L46" s="6" t="s">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3">
-        <v>49123</v>
-      </c>
-      <c r="S46" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
@@ -4363,7 +4565,7 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AA46" s="3" t="s">
         <v>41</v>
@@ -4377,7 +4579,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026090074</v>
+        <v>2026090632</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4386,44 +4588,42 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
       <c r="L47" s="8" t="s">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
       <c r="R47" s="7">
-        <v>61971</v>
-      </c>
-      <c r="S47" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
@@ -4431,7 +4631,7 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AA47" s="7" t="s">
         <v>41</v>
@@ -4445,7 +4645,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026090079</v>
+        <v>2026090652</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4454,44 +4654,42 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>91</v>
+        <v>211</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
       <c r="L48" s="6" t="s">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3">
-        <v>39446</v>
-      </c>
-      <c r="S48" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
@@ -4499,7 +4697,7 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>41</v>
@@ -4513,7 +4711,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026090073</v>
+        <v>2026090392</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4522,42 +4720,42 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="P49" s="7"/>
       <c r="Q49" s="7"/>
       <c r="R49" s="7">
-        <v>45148</v>
+        <v>0</v>
       </c>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
@@ -4567,7 +4765,7 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="AA49" s="7" t="s">
         <v>41</v>
@@ -4581,7 +4779,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026090072</v>
+        <v>2026090309</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4590,44 +4788,42 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M50" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="J50" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="M50" s="6" t="s">
+      <c r="N50" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="N50" s="6" t="s">
-        <v>225</v>
-      </c>
       <c r="O50" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3">
-        <v>23897</v>
-      </c>
-      <c r="S50" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
@@ -4635,7 +4831,7 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AA50" s="3" t="s">
         <v>41</v>
@@ -4649,7 +4845,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026090406</v>
+        <v>2026090240</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -4658,22 +4854,22 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>212</v>
+        <v>119</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>227</v>
+        <v>46</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
@@ -4688,12 +4884,14 @@
         <v>230</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
+      <c r="Q51" s="7">
+        <v>1900</v>
+      </c>
       <c r="R51" s="7">
-        <v>124253</v>
+        <v>28500</v>
       </c>
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
@@ -4703,7 +4901,7 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="AA51" s="7" t="s">
         <v>41</v>
@@ -4717,7 +4915,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026090078</v>
+        <v>2026090256</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -4726,42 +4924,44 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>208</v>
+        <v>119</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>227</v>
+        <v>46</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>201</v>
+        <v>47</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
+      <c r="Q52" s="3">
+        <v>6432</v>
+      </c>
       <c r="R52" s="3">
-        <v>1150</v>
+        <v>770</v>
       </c>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
@@ -4785,7 +4985,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026090076</v>
+        <v>2026090405</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4794,42 +4994,44 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>227</v>
+        <v>46</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>201</v>
+        <v>47</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="O53" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P53" s="7"/>
-      <c r="Q53" s="7"/>
+      <c r="Q53" s="7">
+        <v>770</v>
+      </c>
       <c r="R53" s="7">
-        <v>6813</v>
+        <v>6432</v>
       </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
@@ -4839,7 +5041,7 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>50</v>
+        <v>236</v>
       </c>
       <c r="AA53" s="7" t="s">
         <v>41</v>
@@ -4853,7 +5055,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026090477</v>
+        <v>2026090588</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -4862,44 +5064,42 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>188</v>
+        <v>51</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>237</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="M54" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="M54" s="6" t="s">
+      <c r="N54" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P54" s="3"/>
-      <c r="Q54" s="3">
-        <v>2506</v>
-      </c>
+      <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>6417</v>
+        <v>4146</v>
       </c>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
@@ -4909,7 +5109,7 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="AA54" s="3" t="s">
         <v>41</v>
@@ -4923,7 +5123,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026090465</v>
+        <v>2026090071</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -4932,34 +5132,34 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G55" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H55" s="7" t="s">
         <v>240</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>241</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>242</v>
+        <v>160</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L55" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M55" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="M55" s="8" t="s">
+      <c r="N55" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="N55" s="8" t="s">
-        <v>245</v>
       </c>
       <c r="O55" s="7" t="s">
         <v>39</v>
@@ -4967,7 +5167,7 @@
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>53932</v>
+        <v>3953</v>
       </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
@@ -4977,7 +5177,7 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="AA55" s="7" t="s">
         <v>41</v>
@@ -4991,7 +5191,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026090432</v>
+        <v>2026090603</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -5000,34 +5200,34 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>242</v>
+        <v>160</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="M56" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="N56" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>39</v>
@@ -5035,7 +5235,7 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3">
-        <v>30234</v>
+        <v>10</v>
       </c>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
@@ -5045,7 +5245,7 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="AA56" s="3" t="s">
         <v>41</v>
@@ -5059,7 +5259,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026090428</v>
+        <v>2026090587</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5068,34 +5268,34 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G57" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I57" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="H57" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>250</v>
-      </c>
       <c r="J57" s="7" t="s">
-        <v>242</v>
+        <v>59</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="M57" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="N57" s="8" t="s">
         <v>251</v>
-      </c>
-      <c r="N57" s="8" t="s">
-        <v>252</v>
       </c>
       <c r="O57" s="7" t="s">
         <v>39</v>
@@ -5103,7 +5303,7 @@
       <c r="P57" s="7"/>
       <c r="Q57" s="7"/>
       <c r="R57" s="7">
-        <v>130586</v>
+        <v>63226</v>
       </c>
       <c r="S57" s="7"/>
       <c r="T57" s="7"/>
@@ -5113,7 +5313,7 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="AA57" s="7" t="s">
         <v>41</v>
@@ -5127,7 +5327,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026090407</v>
+        <v>2026090075</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5136,34 +5336,34 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>212</v>
+        <v>51</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>249</v>
+        <v>140</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>242</v>
+        <v>59</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="M58" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="N58" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>39</v>
@@ -5171,7 +5371,7 @@
       <c r="P58" s="3"/>
       <c r="Q58" s="3"/>
       <c r="R58" s="3">
-        <v>280656</v>
+        <v>11827</v>
       </c>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
@@ -5181,7 +5381,7 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="6" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>41</v>
@@ -5195,7 +5395,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026090430</v>
+        <v>2026090077</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5204,28 +5404,28 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>143</v>
+        <v>255</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>256</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>242</v>
+        <v>59</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="M59" s="8" t="s">
         <v>257</v>
@@ -5239,7 +5439,7 @@
       <c r="P59" s="7"/>
       <c r="Q59" s="7"/>
       <c r="R59" s="7">
-        <v>212550</v>
+        <v>49123</v>
       </c>
       <c r="S59" s="7"/>
       <c r="T59" s="7"/>
@@ -5249,7 +5449,7 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="8" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="AA59" s="7" t="s">
         <v>41</v>
@@ -5263,7 +5463,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026090466</v>
+        <v>2026090074</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5272,42 +5472,42 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>242</v>
+        <v>59</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3">
-        <v>212550</v>
+        <v>61971</v>
       </c>
       <c r="S60" s="3"/>
       <c r="T60" s="3"/>
@@ -5317,7 +5517,7 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="6" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>41</v>
@@ -5327,37 +5527,1395 @@
       </c>
     </row>
     <row r="61" spans="1:28">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="9"/>
-      <c r="P61" s="9"/>
-      <c r="Q61" s="9"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="9"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="9"/>
-      <c r="V61" s="9"/>
-      <c r="W61" s="9"/>
-      <c r="X61" s="9"/>
-      <c r="Y61" s="9"/>
-      <c r="Z61" s="10"/>
-      <c r="AA61" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="AB61" s="9">
+      <c r="A61" s="7">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7">
+        <v>2026090079</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>42</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="O61" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="7">
+        <v>39446</v>
+      </c>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7"/>
+      <c r="U61" s="7"/>
+      <c r="V61" s="7"/>
+      <c r="W61" s="7"/>
+      <c r="X61" s="7"/>
+      <c r="Y61" s="7"/>
+      <c r="Z61" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA61" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB61" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:28">
+      <c r="A62" s="3">
+        <v>60</v>
+      </c>
+      <c r="B62" s="3">
+        <v>2026090073</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3">
+        <v>45148</v>
+      </c>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
+      <c r="Z62" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:28">
+      <c r="A63" s="7">
+        <v>61</v>
+      </c>
+      <c r="B63" s="7">
+        <v>2026090072</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="N63" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="O63" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7">
+        <v>23897</v>
+      </c>
+      <c r="S63" s="7"/>
+      <c r="T63" s="7"/>
+      <c r="U63" s="7"/>
+      <c r="V63" s="7"/>
+      <c r="W63" s="7"/>
+      <c r="X63" s="7"/>
+      <c r="Y63" s="7"/>
+      <c r="Z63" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA63" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB63" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:28">
+      <c r="A64" s="3">
+        <v>62</v>
+      </c>
+      <c r="B64" s="3">
+        <v>2026090593</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3">
+        <v>586</v>
+      </c>
+      <c r="R64" s="3">
+        <v>43605</v>
+      </c>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
+      <c r="Z64" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA64" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:28">
+      <c r="A65" s="7">
+        <v>63</v>
+      </c>
+      <c r="B65" s="7">
+        <v>2026090406</v>
+      </c>
+      <c r="C65" s="7">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="N65" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="O65" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="7">
+        <v>124253</v>
+      </c>
+      <c r="S65" s="7"/>
+      <c r="T65" s="7"/>
+      <c r="U65" s="7"/>
+      <c r="V65" s="7"/>
+      <c r="W65" s="7"/>
+      <c r="X65" s="7"/>
+      <c r="Y65" s="7"/>
+      <c r="Z65" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA65" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB65" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28">
+      <c r="A66" s="3">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3">
+        <v>2026090078</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3">
+        <v>1150</v>
+      </c>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
+      <c r="Z66" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB66" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28">
+      <c r="A67" s="7">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7">
+        <v>2026090076</v>
+      </c>
+      <c r="C67" s="7">
+        <v>1</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="N67" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="O67" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7">
+        <v>6813</v>
+      </c>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
+      <c r="U67" s="7"/>
+      <c r="V67" s="7"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA67" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB67" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:28">
+      <c r="A68" s="3">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3">
+        <v>2026090477</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3">
+        <v>2506</v>
+      </c>
+      <c r="R68" s="3">
+        <v>6417</v>
+      </c>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
+      <c r="Z68" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA68" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:28">
+      <c r="A69" s="7">
+        <v>67</v>
+      </c>
+      <c r="B69" s="7">
+        <v>2026090465</v>
+      </c>
+      <c r="C69" s="7">
+        <v>1</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="M69" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="N69" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="O69" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="7">
+        <v>53932</v>
+      </c>
+      <c r="S69" s="7"/>
+      <c r="T69" s="7"/>
+      <c r="U69" s="7"/>
+      <c r="V69" s="7"/>
+      <c r="W69" s="7"/>
+      <c r="X69" s="7"/>
+      <c r="Y69" s="7"/>
+      <c r="Z69" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA69" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB69" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:28">
+      <c r="A70" s="3">
+        <v>68</v>
+      </c>
+      <c r="B70" s="3">
+        <v>2026090432</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3">
+        <v>30234</v>
+      </c>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA70" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:28">
+      <c r="A71" s="7">
+        <v>69</v>
+      </c>
+      <c r="B71" s="7">
+        <v>2026090428</v>
+      </c>
+      <c r="C71" s="7">
+        <v>1</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K71" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="M71" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="N71" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="O71" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="7">
+        <v>130586</v>
+      </c>
+      <c r="S71" s="7"/>
+      <c r="T71" s="7"/>
+      <c r="U71" s="7"/>
+      <c r="V71" s="7"/>
+      <c r="W71" s="7"/>
+      <c r="X71" s="7"/>
+      <c r="Y71" s="7"/>
+      <c r="Z71" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA71" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB71" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:28">
+      <c r="A72" s="3">
+        <v>70</v>
+      </c>
+      <c r="B72" s="3">
+        <v>2026090407</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3">
+        <v>280656</v>
+      </c>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
+      <c r="Z72" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB72" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:28">
+      <c r="A73" s="7">
+        <v>71</v>
+      </c>
+      <c r="B73" s="7">
+        <v>2026090430</v>
+      </c>
+      <c r="C73" s="7">
+        <v>1</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K73" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="N73" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="O73" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="7">
+        <v>212550</v>
+      </c>
+      <c r="S73" s="7"/>
+      <c r="T73" s="7"/>
+      <c r="U73" s="7"/>
+      <c r="V73" s="7"/>
+      <c r="W73" s="7"/>
+      <c r="X73" s="7"/>
+      <c r="Y73" s="7"/>
+      <c r="Z73" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA73" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB73" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28">
+      <c r="A74" s="3">
+        <v>72</v>
+      </c>
+      <c r="B74" s="3">
+        <v>2026090466</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3">
+        <v>212550</v>
+      </c>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
+      <c r="Z74" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA74" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:28">
+      <c r="A75" s="7">
+        <v>73</v>
+      </c>
+      <c r="B75" s="7">
+        <v>2026090639</v>
+      </c>
+      <c r="C75" s="7">
+        <v>1</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="I75" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K75" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="M75" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="N75" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="O75" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
+      <c r="R75" s="7">
+        <v>162634</v>
+      </c>
+      <c r="S75" s="7"/>
+      <c r="T75" s="7"/>
+      <c r="U75" s="7"/>
+      <c r="V75" s="7"/>
+      <c r="W75" s="7"/>
+      <c r="X75" s="7"/>
+      <c r="Y75" s="7"/>
+      <c r="Z75" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA75" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB75" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:28">
+      <c r="A76" s="3">
+        <v>74</v>
+      </c>
+      <c r="B76" s="3">
+        <v>2026090586</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3">
+        <v>51037</v>
+      </c>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
+      <c r="Z76" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB76" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:28">
+      <c r="A77" s="7">
+        <v>75</v>
+      </c>
+      <c r="B77" s="7">
+        <v>2026090585</v>
+      </c>
+      <c r="C77" s="7">
+        <v>1</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="M77" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="N77" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="O77" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
+      <c r="R77" s="7">
+        <v>508479</v>
+      </c>
+      <c r="S77" s="7"/>
+      <c r="T77" s="7"/>
+      <c r="U77" s="7"/>
+      <c r="V77" s="7"/>
+      <c r="W77" s="7"/>
+      <c r="X77" s="7"/>
+      <c r="Y77" s="7"/>
+      <c r="Z77" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="AA77" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB77" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:28">
+      <c r="A78" s="3">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3">
+        <v>2026090635</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3">
+        <v>0</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
+      <c r="Z78" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA78" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB78" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:28">
+      <c r="A79" s="7">
+        <v>77</v>
+      </c>
+      <c r="B79" s="7">
+        <v>2026090469</v>
+      </c>
+      <c r="C79" s="7">
+        <v>1</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="N79" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
+      <c r="R79" s="7">
+        <v>0</v>
+      </c>
+      <c r="S79" s="7"/>
+      <c r="T79" s="7"/>
+      <c r="U79" s="7"/>
+      <c r="V79" s="7"/>
+      <c r="W79" s="7"/>
+      <c r="X79" s="7"/>
+      <c r="Y79" s="7"/>
+      <c r="Z79" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="AA79" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB79" s="7"/>
+    </row>
+    <row r="80" spans="1:28">
+      <c r="A80" s="3">
+        <v>78</v>
+      </c>
+      <c r="B80" s="3">
+        <v>2026090634</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3">
+        <v>0</v>
+      </c>
+      <c r="S80" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
+      <c r="Z80" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA80" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28">
+      <c r="A81" s="9"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="9"/>
+      <c r="P81" s="9"/>
+      <c r="Q81" s="9"/>
+      <c r="R81" s="9"/>
+      <c r="S81" s="9"/>
+      <c r="T81" s="9"/>
+      <c r="U81" s="9"/>
+      <c r="V81" s="9"/>
+      <c r="W81" s="9"/>
+      <c r="X81" s="9"/>
+      <c r="Y81" s="9"/>
+      <c r="Z81" s="10"/>
+      <c r="AA81" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB81" s="9">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202609_Service_Count_Report.xlsx
+++ b/IM/202609_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$113</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="420">
   <si>
     <t>服務次數統計表        篩選月份：202609</t>
   </si>
@@ -158,6 +158,30 @@
     <t>O</t>
   </si>
   <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>09:50:00</t>
+  </si>
+  <si>
+    <t>10:15:00</t>
+  </si>
+  <si>
+    <t>T251000083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台灣佳耐美電子科技股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區員山路512-7號3樓</t>
+  </si>
+  <si>
+    <t>服務</t>
+  </si>
+  <si>
+    <t>Pm</t>
+  </si>
+  <si>
     <t>2026-09-01</t>
   </si>
   <si>
@@ -182,15 +206,6 @@
     <t>中和</t>
   </si>
   <si>
-    <t>Pm</t>
-  </si>
-  <si>
-    <t>09:50:00</t>
-  </si>
-  <si>
-    <t>10:15:00</t>
-  </si>
-  <si>
     <t>T252000150</t>
   </si>
   <si>
@@ -200,9 +215,6 @@
     <t>士林</t>
   </si>
   <si>
-    <t>服務</t>
-  </si>
-  <si>
     <t>10:12:00</t>
   </si>
   <si>
@@ -224,6 +236,27 @@
     <t>2026-09-03</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>15:15:00</t>
+  </si>
+  <si>
+    <t>T302800057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呈慈文理補習班 </t>
+  </si>
+  <si>
+    <t>新北市永和區保生路48巷5號1樓</t>
+  </si>
+  <si>
+    <t>維修</t>
+  </si>
+  <si>
+    <t>清潔放電座</t>
+  </si>
+  <si>
     <t>09:53:00</t>
   </si>
   <si>
@@ -281,12 +314,25 @@
     <t>三重義天店</t>
   </si>
   <si>
-    <t>維修</t>
-  </si>
-  <si>
     <t xml:space="preserve">7號網路線差在Mmk這端水晶頭沒卡好 已建議店家更換7號網路線 </t>
   </si>
   <si>
+    <t>13:06:00</t>
+  </si>
+  <si>
+    <t>THILF02543</t>
+  </si>
+  <si>
+    <t>新北市三重區大仁街78號</t>
+  </si>
+  <si>
+    <t>三重大仁店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2PORT改插回1PORT Hub
+</t>
+  </si>
+  <si>
     <t>10:30:00</t>
   </si>
   <si>
@@ -326,6 +372,24 @@
     <t>換下8119010711 換上8119011879</t>
   </si>
   <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>12:02:00</t>
+  </si>
+  <si>
+    <t>THILF03623</t>
+  </si>
+  <si>
+    <t>新北市三重區自強路二段74巷1號及特76號</t>
+  </si>
+  <si>
+    <t>三重自強店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">螢幕排線重新插拔 可正常點擊 </t>
+  </si>
+  <si>
     <t>10:35:00</t>
   </si>
   <si>
@@ -371,6 +435,21 @@
     <t>北縣天龍店</t>
   </si>
   <si>
+    <t>THILF04101</t>
+  </si>
+  <si>
+    <t>新北市三重區溪尾街293號及295號</t>
+  </si>
+  <si>
+    <t>三重溪華店</t>
+  </si>
+  <si>
+    <t>換下8155003807 換上8155004451</t>
+  </si>
+  <si>
+    <t>11:20:00</t>
+  </si>
+  <si>
     <t>13:20:00</t>
   </si>
   <si>
@@ -399,6 +478,42 @@
   </si>
   <si>
     <t>三重公園店</t>
+  </si>
+  <si>
+    <t>18:36:00</t>
+  </si>
+  <si>
+    <t>18:56:00</t>
+  </si>
+  <si>
+    <t>THILF0C052</t>
+  </si>
+  <si>
+    <t>新北市中和區連城路47巷1號</t>
+  </si>
+  <si>
+    <t>中和連城店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">影印機傳真電話線插電話無任何反應 已請店家改報修中華電信 </t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>15:35:00</t>
+  </si>
+  <si>
+    <t>THILF0C192</t>
+  </si>
+  <si>
+    <t>新北市中和區莊敬路29號</t>
+  </si>
+  <si>
+    <t>中和福美店</t>
+  </si>
+  <si>
+    <t>改裝撤機</t>
   </si>
   <si>
     <t>13:00:00</t>
@@ -528,9 +643,6 @@
     <t>11:00:00</t>
   </si>
   <si>
-    <t>11:20:00</t>
-  </si>
-  <si>
     <t>T302800006</t>
   </si>
   <si>
@@ -540,9 +652,6 @@
     <t>新北市淡水區民族路50巷46號3樓</t>
   </si>
   <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
     <t>15:50:00</t>
   </si>
   <si>
@@ -615,6 +724,21 @@
     <t>蘆竹</t>
   </si>
   <si>
+    <t>15:12:00</t>
+  </si>
+  <si>
+    <t>T352500149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東南旅行社股份有限公司 </t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區忠孝東路17之3號(南崁分公司</t>
+  </si>
+  <si>
+    <t>南崁分公司</t>
+  </si>
+  <si>
     <t>14:50:00</t>
   </si>
   <si>
@@ -628,6 +752,30 @@
   </si>
   <si>
     <t>林口文化1F營業部</t>
+  </si>
+  <si>
+    <t>T501500008</t>
+  </si>
+  <si>
+    <t>eS-5015AC 彩色複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">輔仁大學學校財團法人輔仁大學附設醫 </t>
+  </si>
+  <si>
+    <t>新北市泰山區貴子路69號B1(病例組)</t>
+  </si>
+  <si>
+    <t>病例組</t>
+  </si>
+  <si>
+    <t>T501500009</t>
+  </si>
+  <si>
+    <t>新北市泰山區貴子路69號B1(保險組)</t>
+  </si>
+  <si>
+    <t>保險組左</t>
   </si>
   <si>
     <t>THILF02596</t>
@@ -710,10 +858,37 @@
     <t>龜山A8站</t>
   </si>
   <si>
+    <t>15:36:00</t>
+  </si>
+  <si>
+    <t>裝潢撤機已完工</t>
+  </si>
+  <si>
+    <t>THILF0F777</t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區南華一街1號</t>
+  </si>
+  <si>
+    <t>蘆竹南華店</t>
+  </si>
+  <si>
     <t>湯家瑋</t>
   </si>
   <si>
-    <t>14:30:00</t>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>T252000086</t>
+  </si>
+  <si>
+    <t>新北市三重區仁義街79巷旁工地</t>
+  </si>
+  <si>
+    <t>華固慕川</t>
+  </si>
+  <si>
+    <t>pm</t>
   </si>
   <si>
     <t>T252000102</t>
@@ -731,6 +906,15 @@
     <t>列印文字異常 更換PS3驅動</t>
   </si>
   <si>
+    <t>T252000113</t>
+  </si>
+  <si>
+    <t>新北市三重區仁義街與元信一街交叉口</t>
+  </si>
+  <si>
+    <t>華固織幸</t>
+  </si>
+  <si>
     <t>T252000136</t>
   </si>
   <si>
@@ -743,7 +927,10 @@
     <t>09:00:00</t>
   </si>
   <si>
-    <t>pm</t>
+    <t>16:15:00</t>
+  </si>
+  <si>
+    <t>送發票</t>
   </si>
   <si>
     <t>T301800009</t>
@@ -779,6 +966,48 @@
     <t>五股倉庫(黑)</t>
   </si>
   <si>
+    <t>T301800171</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正區336-1號(新莊)</t>
+  </si>
+  <si>
+    <t>新莊</t>
+  </si>
+  <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>T301800174</t>
+  </si>
+  <si>
+    <t>新北市板橋區中山路1段10號5樓(板橋分校)</t>
+  </si>
+  <si>
+    <t>板橋</t>
+  </si>
+  <si>
+    <t>T302800007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">財團法人台灣省私立台灣盲人重建院 </t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路384號3樓</t>
+  </si>
+  <si>
+    <t>3F</t>
+  </si>
+  <si>
+    <t>T302800008</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路384號4樓</t>
+  </si>
+  <si>
+    <t>4F</t>
+  </si>
+  <si>
     <t>09:10:00</t>
   </si>
   <si>
@@ -791,6 +1020,12 @@
     <t>三重湯城4樓(黑)J22</t>
   </si>
   <si>
+    <t>13:45:00</t>
+  </si>
+  <si>
+    <t>碳粉</t>
+  </si>
+  <si>
     <t>T302800053</t>
   </si>
   <si>
@@ -800,6 +1035,12 @@
     <t>業務部辦公室</t>
   </si>
   <si>
+    <t>T302800123</t>
+  </si>
+  <si>
+    <t>新北市三重區正義北路218號(三重分校)</t>
+  </si>
+  <si>
     <t>10:50:00</t>
   </si>
   <si>
@@ -923,9 +1164,6 @@
     <t>五股4樓</t>
   </si>
   <si>
-    <t>10:00:00</t>
-  </si>
-  <si>
     <t>T352800030</t>
   </si>
   <si>
@@ -956,6 +1194,9 @@
     <t>卡紙更換取送分x4</t>
   </si>
   <si>
+    <t>更換取送分</t>
+  </si>
+  <si>
     <t>T452800007</t>
   </si>
   <si>
@@ -971,6 +1212,9 @@
     <t>送碳粉 更換OD OD刮回刮 上熱</t>
   </si>
   <si>
+    <t>碳粉 OD OD刮 回刮 上熱</t>
+  </si>
+  <si>
     <t>T452800031</t>
   </si>
   <si>
@@ -984,6 +1228,36 @@
   </si>
   <si>
     <t>台北客服4樓-2LJ15(黑)</t>
+  </si>
+  <si>
+    <t>14:15:00</t>
+  </si>
+  <si>
+    <t>T452800069</t>
+  </si>
+  <si>
+    <t>台北客服4樓-2LJ6(黑)</t>
+  </si>
+  <si>
+    <t>TX81000001</t>
+  </si>
+  <si>
+    <t>TCx810 POS 終端系統</t>
+  </si>
+  <si>
+    <t>POS商品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日商樂比亞股份有限公司台灣分公司 </t>
+  </si>
+  <si>
+    <t>新北市新莊區新北大道4段3號B2</t>
+  </si>
+  <si>
+    <t>新莊宏匯店</t>
+  </si>
+  <si>
+    <t>場地勘察</t>
   </si>
   <si>
     <t>狄澤洋</t>
@@ -1433,7 +1707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB81"/>
+  <dimension ref="A1:AB113"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -1659,7 +1933,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <v>2026090305</v>
+        <v>2026090874</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -1683,31 +1957,33 @@
         <v>45</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6"/>
+      <c r="O4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3">
+        <v>220</v>
+      </c>
       <c r="Q4" s="3">
-        <v>5118</v>
+        <v>10659</v>
       </c>
       <c r="R4" s="3">
-        <v>21005</v>
-      </c>
-      <c r="S4" s="3"/>
+        <v>62711</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -1715,7 +1991,7 @@
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA4" s="3" t="s">
         <v>41</v>
@@ -1729,7 +2005,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7">
-        <v>2026090043</v>
+        <v>2026090305</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -1741,7 +2017,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>51</v>
@@ -1753,33 +2029,31 @@
         <v>53</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7">
-        <v>4289</v>
+        <v>5118</v>
       </c>
       <c r="R5" s="7">
-        <v>3065</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>21005</v>
+      </c>
+      <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
@@ -1787,7 +2061,7 @@
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA5" s="7" t="s">
         <v>41</v>
@@ -1801,7 +2075,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>2026090044</v>
+        <v>2026090043</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1813,34 +2087,34 @@
         <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3">
@@ -1849,7 +2123,9 @@
       <c r="R6" s="3">
         <v>3065</v>
       </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -1857,19 +2133,21 @@
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB6" s="3"/>
+      <c r="AB6" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:28">
       <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="7">
-        <v>2026090412</v>
+        <v>2026090044</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -1881,43 +2159,43 @@
         <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>58</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="M7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>62</v>
-      </c>
       <c r="O7" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
+      <c r="Q7" s="7">
+        <v>4289</v>
+      </c>
       <c r="R7" s="7">
-        <v>85015</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>3065</v>
+      </c>
+      <c r="S7" s="7"/>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -1925,21 +2203,19 @@
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB7" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB7" s="7"/>
     </row>
     <row r="8" spans="1:28">
       <c r="A8" s="3">
         <v>6</v>
       </c>
       <c r="B8" s="3">
-        <v>2026090602</v>
+        <v>2026090412</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1951,41 +2227,43 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="O8" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3">
-        <v>42846</v>
-      </c>
-      <c r="S8" s="3"/>
+        <v>85015</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -1993,7 +2271,7 @@
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="6" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>41</v>
@@ -2007,7 +2285,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7">
-        <v>2026090599</v>
+        <v>2026090633</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -2019,39 +2297,37 @@
         <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>59</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="8"/>
+      <c r="O9" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7">
-        <v>17803</v>
+        <v>15926</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -2075,7 +2351,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="3">
-        <v>2026090226</v>
+        <v>2026090602</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -2087,39 +2363,39 @@
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>75</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="M10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="N10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="O10" s="3" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>42846</v>
       </c>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -2129,7 +2405,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AA10" s="3" t="s">
         <v>41</v>
@@ -2143,7 +2419,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026090431</v>
+        <v>2026090599</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -2155,49 +2431,49 @@
         <v>30</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+        <v>82</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L11" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7">
-        <v>0</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>17803</v>
+      </c>
+      <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
-      <c r="Y11" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y11" s="7"/>
       <c r="Z11" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA11" s="7" t="s">
         <v>41</v>
@@ -2211,7 +2487,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026090332</v>
+        <v>2026090226</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -2223,49 +2499,49 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="M12" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="N12" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="O12" s="3" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
         <v>0</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
-      <c r="Y12" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y12" s="3"/>
       <c r="Z12" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>41</v>
@@ -2279,7 +2555,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026090057</v>
+        <v>2026090897</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -2294,31 +2570,31 @@
         <v>42</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="7" t="s">
-        <v>93</v>
-      </c>
       <c r="J13" s="7" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
@@ -2333,19 +2609,21 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB13" s="7"/>
+      <c r="AB13" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026090053</v>
+        <v>2026090431</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2357,30 +2635,30 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="6" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -2399,7 +2677,7 @@
         <v>41</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>41</v>
@@ -2413,7 +2691,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026090205</v>
+        <v>2026090332</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2425,30 +2703,30 @@
         <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
@@ -2467,7 +2745,7 @@
         <v>41</v>
       </c>
       <c r="Z15" s="8" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>41</v>
@@ -2481,7 +2759,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026090493</v>
+        <v>2026090057</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2493,63 +2771,61 @@
         <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="J16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M16" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="N16" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="O16" s="3" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3">
         <v>0</v>
       </c>
-      <c r="S16" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y16" s="3"/>
       <c r="Z16" s="6" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB16" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB16" s="3"/>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="7">
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026090468</v>
+        <v>2026090851</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2561,7 +2837,7 @@
         <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>113</v>
@@ -2572,10 +2848,14 @@
       <c r="I17" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
+      <c r="J17" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>90</v>
+      </c>
       <c r="L17" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="M17" s="8" t="s">
         <v>116</v>
@@ -2584,26 +2864,22 @@
         <v>117</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7">
         <v>0</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="S17" s="7"/>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="Y17" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y17" s="7"/>
       <c r="Z17" s="8" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="AA17" s="7" t="s">
         <v>41</v>
@@ -2617,7 +2893,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026090482</v>
+        <v>2026090053</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2629,30 +2905,30 @@
         <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="6" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -2671,7 +2947,7 @@
         <v>41</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>41</v>
@@ -2685,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026090584</v>
+        <v>2026090205</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2697,49 +2973,49 @@
         <v>30</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>79</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
       <c r="L19" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7">
         <v>0</v>
       </c>
-      <c r="S19" s="7"/>
+      <c r="S19" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T19" s="7"/>
       <c r="U19" s="7"/>
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
+      <c r="Y19" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z19" s="8" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>41</v>
@@ -2753,7 +3029,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026090213</v>
+        <v>2026090493</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2765,7 +3041,7 @@
         <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>129</v>
@@ -2779,7 +3055,7 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="6" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>132</v>
@@ -2788,7 +3064,7 @@
         <v>133</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
@@ -2807,7 +3083,7 @@
         <v>41</v>
       </c>
       <c r="Z20" s="6" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>41</v>
@@ -2821,7 +3097,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026090475</v>
+        <v>2026090592</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -2833,49 +3109,49 @@
         <v>30</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G21" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="J21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M21" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="N21" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="O21" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
       <c r="R21" s="7">
         <v>0</v>
       </c>
-      <c r="S21" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="S21" s="7"/>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
-      <c r="Y21" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="Y21" s="7"/>
       <c r="Z21" s="8" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>41</v>
@@ -2889,7 +3165,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026090613</v>
+        <v>2026090882</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -2898,46 +3174,38 @@
         <v>29</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
       <c r="L22" s="6" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P22" s="3">
-        <v>8173</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>18275</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
       <c r="R22" s="3">
-        <v>26694</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>41</v>
@@ -2947,23 +3215,23 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
+      <c r="Y22" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z22" s="6" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB22" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB22" s="3"/>
     </row>
     <row r="23" spans="1:28">
       <c r="A23" s="7">
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026090614</v>
+        <v>2026090468</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -2972,13 +3240,13 @@
         <v>29</v>
       </c>
       <c r="E23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>140</v>
@@ -2986,14 +3254,10 @@
       <c r="I23" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="J23" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
       <c r="L23" s="8" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="M23" s="8" t="s">
         <v>142</v>
@@ -3002,38 +3266,40 @@
         <v>143</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P23" s="7">
-        <v>8173</v>
-      </c>
-      <c r="Q23" s="7">
-        <v>18275</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
       <c r="R23" s="7">
-        <v>26694</v>
-      </c>
-      <c r="S23" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
+      <c r="Y23" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z23" s="8" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AA23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB23" s="7"/>
+      <c r="AB23" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026090242</v>
+        <v>2026090482</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -3042,13 +3308,13 @@
         <v>29</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>145</v>
@@ -3056,54 +3322,52 @@
       <c r="I24" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
       <c r="L24" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="N24" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="N24" s="6" t="s">
-        <v>149</v>
-      </c>
       <c r="O24" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P24" s="3"/>
-      <c r="Q24" s="3">
-        <v>3064</v>
-      </c>
+      <c r="Q24" s="3"/>
       <c r="R24" s="3">
-        <v>165868</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="T24" s="3"/>
-      <c r="U24" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
+      <c r="Y24" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z24" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:28">
       <c r="A25" s="7">
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026090243</v>
+        <v>2026090714</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -3112,44 +3376,42 @@
         <v>29</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="P25" s="7"/>
-      <c r="Q25" s="7">
-        <v>3064</v>
-      </c>
+      <c r="Q25" s="7"/>
       <c r="R25" s="7">
-        <v>165868</v>
+        <v>0</v>
       </c>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -3159,17 +3421,21 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="AA25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB25" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026090498</v>
+        <v>2026090921</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -3178,52 +3444,50 @@
         <v>29</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
       <c r="L26" s="6" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="N26" s="6"/>
+        <v>158</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>159</v>
+      </c>
       <c r="O26" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="P26" s="3"/>
-      <c r="Q26" s="3">
-        <v>667</v>
-      </c>
+      <c r="Q26" s="3"/>
       <c r="R26" s="3">
-        <v>29333</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
+      <c r="T26" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>41</v>
@@ -3237,7 +3501,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026090496</v>
+        <v>2026090584</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -3246,46 +3510,44 @@
         <v>29</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="N27" s="8"/>
+        <v>164</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="O27" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="P27" s="7"/>
-      <c r="Q27" s="7">
-        <v>667</v>
-      </c>
+      <c r="Q27" s="7"/>
       <c r="R27" s="7">
-        <v>29333</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S27" s="7"/>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
@@ -3293,19 +3555,21 @@
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="AA27" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB27" s="7"/>
+      <c r="AB27" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="3">
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026090497</v>
+        <v>2026090213</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -3314,64 +3578,66 @@
         <v>29</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
       <c r="L28" s="6" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="N28" s="6"/>
+        <v>170</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="O28" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P28" s="3"/>
-      <c r="Q28" s="3">
-        <v>667</v>
-      </c>
+      <c r="Q28" s="3"/>
       <c r="R28" s="3">
-        <v>29333</v>
-      </c>
-      <c r="S28" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
+      <c r="Y28" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="Z28" s="6" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AA28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB28" s="3"/>
+      <c r="AB28" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="7">
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026090459</v>
+        <v>2026090475</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3380,42 +3646,38 @@
         <v>29</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
       <c r="L29" s="8" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="O29" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
       <c r="R29" s="7">
-        <v>30655</v>
+        <v>0</v>
       </c>
       <c r="S29" s="7" t="s">
         <v>41</v>
@@ -3425,9 +3687,11 @@
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
+      <c r="Y29" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="Z29" s="8" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>41</v>
@@ -3441,7 +3705,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026090460</v>
+        <v>2026090613</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3450,44 +3714,50 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>160</v>
+        <v>54</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>161</v>
+        <v>37</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
+        <v>48</v>
+      </c>
+      <c r="P30" s="3">
+        <v>8173</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>18275</v>
+      </c>
       <c r="R30" s="3">
-        <v>30655</v>
-      </c>
-      <c r="S30" s="3"/>
+        <v>26694</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -3495,19 +3765,21 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="AA30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB30" s="3"/>
+      <c r="AB30" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:28">
       <c r="A31" s="7">
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026090453</v>
+        <v>2026090614</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3516,44 +3788,48 @@
         <v>29</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>167</v>
+        <v>37</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="N31" s="8"/>
+        <v>180</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>181</v>
+      </c>
       <c r="O31" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="P31" s="7">
+        <v>8173</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>18275</v>
+      </c>
       <c r="R31" s="7">
-        <v>39400</v>
-      </c>
-      <c r="S31" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>26694</v>
+      </c>
+      <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
@@ -3561,21 +3837,19 @@
       <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="8" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="AA31" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB31" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB31" s="7"/>
     </row>
     <row r="32" spans="1:28">
       <c r="A32" s="3">
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026090454</v>
+        <v>2026090242</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3584,54 +3858,60 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="N32" s="6"/>
+        <v>186</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>187</v>
+      </c>
       <c r="O32" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
+      <c r="Q32" s="3">
+        <v>3064</v>
+      </c>
       <c r="R32" s="3">
-        <v>39400</v>
-      </c>
-      <c r="S32" s="3"/>
+        <v>165868</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
+      <c r="U32" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
     </row>
     <row r="33" spans="1:28">
@@ -3639,7 +3919,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026090286</v>
+        <v>2026090243</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3648,56 +3928,54 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
+      <c r="Q33" s="7">
+        <v>3064</v>
+      </c>
       <c r="R33" s="7">
-        <v>145888</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>165868</v>
+      </c>
+      <c r="S33" s="7"/>
       <c r="T33" s="7"/>
-      <c r="U33" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U33" s="7"/>
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="AA33" s="7"/>
       <c r="AB33" s="7"/>
@@ -3707,7 +3985,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026090287</v>
+        <v>2026090498</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3716,42 +3994,42 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>174</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N34" s="6"/>
       <c r="O34" s="3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
+      <c r="Q34" s="3">
+        <v>667</v>
+      </c>
       <c r="R34" s="3">
-        <v>145888</v>
+        <v>29333</v>
       </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
@@ -3761,17 +4039,21 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA34" s="3"/>
-      <c r="AB34" s="3"/>
+        <v>193</v>
+      </c>
+      <c r="AA34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:28">
       <c r="A35" s="7">
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026090628</v>
+        <v>2026090496</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3780,42 +4062,42 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="N35" s="8" t="s">
-        <v>179</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N35" s="8"/>
       <c r="O35" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
+      <c r="Q35" s="7">
+        <v>667</v>
+      </c>
       <c r="R35" s="7">
-        <v>12306</v>
+        <v>29333</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>41</v>
@@ -3827,9 +4109,11 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA35" s="7"/>
+        <v>182</v>
+      </c>
+      <c r="AA35" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
@@ -3837,7 +4121,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026090629</v>
+        <v>2026090497</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3846,42 +4130,42 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>179</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N36" s="6"/>
       <c r="O36" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
+      <c r="Q36" s="3">
+        <v>667</v>
+      </c>
       <c r="R36" s="3">
-        <v>12306</v>
+        <v>29333</v>
       </c>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
@@ -3891,7 +4175,7 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="AA36" s="3" t="s">
         <v>41</v>
@@ -3903,7 +4187,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026090284</v>
+        <v>2026090459</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -3912,66 +4196,68 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
       <c r="R37" s="7">
-        <v>11283</v>
+        <v>30655</v>
       </c>
       <c r="S37" s="7" t="s">
         <v>41</v>
       </c>
       <c r="T37" s="7"/>
-      <c r="U37" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U37" s="7"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA37" s="7"/>
-      <c r="AB37" s="7"/>
+        <v>182</v>
+      </c>
+      <c r="AA37" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB37" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:28">
       <c r="A38" s="3">
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026090285</v>
+        <v>2026090460</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -3980,34 +4266,34 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>108</v>
+        <v>195</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="O38" s="3" t="s">
         <v>39</v>
@@ -4015,7 +4301,7 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3">
-        <v>11283</v>
+        <v>30655</v>
       </c>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
@@ -4025,9 +4311,11 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA38" s="3"/>
+        <v>182</v>
+      </c>
+      <c r="AA38" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB38" s="3"/>
     </row>
     <row r="39" spans="1:28">
@@ -4035,7 +4323,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026090457</v>
+        <v>2026090453</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -4044,44 +4332,40 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>163</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N39" s="8"/>
       <c r="O39" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P39" s="7"/>
-      <c r="Q39" s="7">
-        <v>3170</v>
-      </c>
+      <c r="Q39" s="7"/>
       <c r="R39" s="7">
-        <v>425348</v>
+        <v>39400</v>
       </c>
       <c r="S39" s="7" t="s">
         <v>41</v>
@@ -4093,7 +4377,7 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="AA39" s="7" t="s">
         <v>41</v>
@@ -4107,7 +4391,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026090458</v>
+        <v>2026090454</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -4116,44 +4400,40 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>184</v>
+        <v>63</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>163</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N40" s="6"/>
       <c r="O40" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P40" s="3"/>
-      <c r="Q40" s="3">
-        <v>3170</v>
-      </c>
+      <c r="Q40" s="3"/>
       <c r="R40" s="3">
-        <v>425348</v>
+        <v>39400</v>
       </c>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
@@ -4163,7 +4443,7 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="AA40" s="3" t="s">
         <v>41</v>
@@ -4175,7 +4455,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026090051</v>
+        <v>2026090286</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -4184,70 +4464,66 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P41" s="7"/>
-      <c r="Q41" s="7">
-        <v>121</v>
-      </c>
+      <c r="Q41" s="7"/>
       <c r="R41" s="7">
-        <v>191</v>
+        <v>145888</v>
       </c>
       <c r="S41" s="7" t="s">
         <v>41</v>
       </c>
       <c r="T41" s="7"/>
-      <c r="U41" s="7"/>
+      <c r="U41" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA41" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB41" s="7">
-        <v>1</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
     </row>
     <row r="42" spans="1:28">
       <c r="A42" s="3">
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026090052</v>
+        <v>2026090287</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4256,44 +4532,42 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P42" s="3"/>
-      <c r="Q42" s="3">
-        <v>121</v>
-      </c>
+      <c r="Q42" s="3"/>
       <c r="R42" s="3">
-        <v>191</v>
+        <v>145888</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
@@ -4303,11 +4577,9 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
     </row>
     <row r="43" spans="1:28">
@@ -4315,7 +4587,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026090244</v>
+        <v>2026090628</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4324,56 +4596,54 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="N43" s="8" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>270931</v>
+        <v>12306</v>
       </c>
       <c r="S43" s="7" t="s">
         <v>41</v>
       </c>
       <c r="T43" s="7"/>
-      <c r="U43" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="AA43" s="7"/>
       <c r="AB43" s="7"/>
@@ -4383,7 +4653,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026090245</v>
+        <v>2026090629</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4392,34 +4662,34 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>39</v>
@@ -4427,7 +4697,7 @@
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>270931</v>
+        <v>12306</v>
       </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
@@ -4437,9 +4707,11 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA44" s="3"/>
+        <v>182</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="AB44" s="3"/>
     </row>
     <row r="45" spans="1:28">
@@ -4447,7 +4719,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026090208</v>
+        <v>2026090284</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4456,64 +4728,66 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
+        <v>216</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L45" s="8" t="s">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7">
-        <v>0</v>
-      </c>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="U45" s="7"/>
+        <v>11283</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V45" s="7"/>
       <c r="W45" s="7"/>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA45" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB45" s="7">
-        <v>1</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="AA45" s="7"/>
+      <c r="AB45" s="7"/>
     </row>
     <row r="46" spans="1:28">
       <c r="A46" s="3">
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026090656</v>
+        <v>2026090285</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4522,42 +4796,44 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
+      <c r="K46" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L46" s="6" t="s">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>11283</v>
+      </c>
+      <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
@@ -4565,21 +4841,17 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>1</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3"/>
     </row>
     <row r="47" spans="1:28">
       <c r="A47" s="7">
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026090632</v>
+        <v>2026090457</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4588,38 +4860,44 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
+        <v>219</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L47" s="8" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
+      <c r="Q47" s="7">
+        <v>3170</v>
+      </c>
       <c r="R47" s="7">
-        <v>0</v>
+        <v>425348</v>
       </c>
       <c r="S47" s="7" t="s">
         <v>41</v>
@@ -4631,7 +4909,7 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="AA47" s="7" t="s">
         <v>41</v>
@@ -4645,7 +4923,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026090652</v>
+        <v>2026090458</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4654,42 +4932,46 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
+        <v>219</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L48" s="6" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="O48" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
+      <c r="Q48" s="3">
+        <v>3170</v>
+      </c>
       <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>425348</v>
+      </c>
+      <c r="S48" s="3"/>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
@@ -4697,21 +4979,19 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB48" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB48" s="3"/>
     </row>
     <row r="49" spans="1:28">
       <c r="A49" s="7">
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026090392</v>
+        <v>2026090051</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4720,44 +5000,48 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>80</v>
+        <v>227</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="O49" s="7" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="7">
+        <v>121</v>
+      </c>
       <c r="R49" s="7">
-        <v>0</v>
-      </c>
-      <c r="S49" s="7"/>
+        <v>191</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
@@ -4765,7 +5049,7 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="AA49" s="7" t="s">
         <v>41</v>
@@ -4779,7 +5063,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026090309</v>
+        <v>2026090052</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4788,42 +5072,46 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
+        <v>225</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L50" s="6" t="s">
-        <v>80</v>
+        <v>227</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
+      <c r="Q50" s="3">
+        <v>121</v>
+      </c>
       <c r="R50" s="3">
-        <v>0</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
@@ -4831,21 +5119,19 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="AA50" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB50" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB50" s="3"/>
     </row>
     <row r="51" spans="1:28">
       <c r="A51" s="7">
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026090240</v>
+        <v>2026090680</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -4854,46 +5140,48 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G51" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="J51" s="7" t="s">
         <v>226</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7">
-        <v>1900</v>
+        <v>7475</v>
       </c>
       <c r="R51" s="7">
-        <v>28500</v>
-      </c>
-      <c r="S51" s="7"/>
+        <v>41465</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
@@ -4901,21 +5189,17 @@
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="AA51" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB51" s="7">
-        <v>1</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="AA51" s="7"/>
+      <c r="AB51" s="7"/>
     </row>
     <row r="52" spans="1:28">
       <c r="A52" s="3">
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026090256</v>
+        <v>2026090681</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -4924,44 +5208,44 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>47</v>
+        <v>232</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>233</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P52" s="3"/>
       <c r="Q52" s="3">
-        <v>6432</v>
+        <v>7475</v>
       </c>
       <c r="R52" s="3">
-        <v>770</v>
+        <v>41465</v>
       </c>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
@@ -4971,21 +5255,19 @@
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="6" t="s">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB52" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB52" s="3"/>
     </row>
     <row r="53" spans="1:28">
       <c r="A53" s="7">
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026090405</v>
+        <v>2026090244</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -4994,68 +5276,66 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>235</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>46</v>
+        <v>237</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>47</v>
+        <v>185</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O53" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P53" s="7"/>
-      <c r="Q53" s="7">
-        <v>770</v>
-      </c>
+      <c r="Q53" s="7"/>
       <c r="R53" s="7">
-        <v>6432</v>
-      </c>
-      <c r="S53" s="7"/>
+        <v>270931</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T53" s="7"/>
-      <c r="U53" s="7"/>
+      <c r="U53" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="V53" s="7"/>
       <c r="W53" s="7"/>
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA53" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB53" s="7">
-        <v>1</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="AA53" s="7"/>
+      <c r="AB53" s="7"/>
     </row>
     <row r="54" spans="1:28">
       <c r="A54" s="3">
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026090588</v>
+        <v>2026090245</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -5064,28 +5344,28 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>51</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J54" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>238</v>
@@ -5099,7 +5379,7 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>4146</v>
+        <v>270931</v>
       </c>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
@@ -5109,21 +5389,17 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>1</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="AA54" s="3"/>
+      <c r="AB54" s="3"/>
     </row>
     <row r="55" spans="1:28">
       <c r="A55" s="7">
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026090071</v>
+        <v>2026090884</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -5132,22 +5408,22 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>234</v>
+        <v>100</v>
       </c>
       <c r="H55" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I55" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="I55" s="7" t="s">
+      <c r="J55" s="7" t="s">
         <v>241</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>36</v>
@@ -5162,14 +5438,18 @@
         <v>244</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P55" s="7"/>
-      <c r="Q55" s="7"/>
+      <c r="Q55" s="7">
+        <v>4436</v>
+      </c>
       <c r="R55" s="7">
-        <v>3953</v>
-      </c>
-      <c r="S55" s="7"/>
+        <v>232948</v>
+      </c>
+      <c r="S55" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
@@ -5177,21 +5457,17 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA55" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB55" s="7">
-        <v>1</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="AA55" s="7"/>
+      <c r="AB55" s="7"/>
     </row>
     <row r="56" spans="1:28">
       <c r="A56" s="3">
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026090603</v>
+        <v>2026090885</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -5200,42 +5476,44 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
+      <c r="Q56" s="3">
+        <v>4436</v>
+      </c>
       <c r="R56" s="3">
-        <v>10</v>
+        <v>232948</v>
       </c>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
@@ -5245,21 +5523,19 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>236</v>
+        <v>182</v>
       </c>
       <c r="AA56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB56" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB56" s="3"/>
     </row>
     <row r="57" spans="1:28">
       <c r="A57" s="7">
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026090587</v>
+        <v>2026090886</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5268,44 +5544,48 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>248</v>
+        <v>124</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="O57" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P57" s="7"/>
-      <c r="Q57" s="7"/>
+      <c r="Q57" s="7">
+        <v>11987</v>
+      </c>
       <c r="R57" s="7">
-        <v>63226</v>
-      </c>
-      <c r="S57" s="7"/>
+        <v>311414</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
       <c r="V57" s="7"/>
@@ -5313,21 +5593,17 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA57" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB57" s="7">
-        <v>1</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="AA57" s="7"/>
+      <c r="AB57" s="7"/>
     </row>
     <row r="58" spans="1:28">
       <c r="A58" s="3">
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026090075</v>
+        <v>2026090887</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5336,22 +5612,22 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>36</v>
@@ -5360,18 +5636,20 @@
         <v>242</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P58" s="3"/>
-      <c r="Q58" s="3"/>
+      <c r="Q58" s="3">
+        <v>11987</v>
+      </c>
       <c r="R58" s="3">
-        <v>11827</v>
+        <v>311414</v>
       </c>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
@@ -5381,21 +5659,19 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="6" t="s">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AB58" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB58" s="3"/>
     </row>
     <row r="59" spans="1:28">
       <c r="A59" s="7">
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026090077</v>
+        <v>2026090208</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5404,52 +5680,50 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>255</v>
+        <v>33</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K59" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
       <c r="L59" s="8" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="N59" s="8" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="O59" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P59" s="7"/>
       <c r="Q59" s="7"/>
       <c r="R59" s="7">
-        <v>49123</v>
+        <v>0</v>
       </c>
       <c r="S59" s="7"/>
-      <c r="T59" s="7"/>
+      <c r="T59" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
       <c r="W59" s="7"/>
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="8" t="s">
-        <v>50</v>
+        <v>251</v>
       </c>
       <c r="AA59" s="7" t="s">
         <v>41</v>
@@ -5463,7 +5737,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026090074</v>
+        <v>2026090656</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5472,44 +5746,42 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
       <c r="L60" s="6" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P60" s="3"/>
       <c r="Q60" s="3"/>
       <c r="R60" s="3">
-        <v>61971</v>
-      </c>
-      <c r="S60" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
@@ -5517,7 +5789,7 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="6" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>41</v>
@@ -5531,7 +5803,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026090079</v>
+        <v>2026090632</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5540,44 +5812,42 @@
         <v>29</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>103</v>
+        <v>255</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>32</v>
+        <v>256</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K61" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
       <c r="L61" s="8" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
       <c r="R61" s="7">
-        <v>39446</v>
-      </c>
-      <c r="S61" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S61" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
@@ -5585,7 +5855,7 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="8" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="AA61" s="7" t="s">
         <v>41</v>
@@ -5599,7 +5869,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026090073</v>
+        <v>2026090652</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -5608,44 +5878,42 @@
         <v>29</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>70</v>
+        <v>261</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3"/>
       <c r="L62" s="6" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P62" s="3"/>
       <c r="Q62" s="3"/>
       <c r="R62" s="3">
-        <v>45148</v>
-      </c>
-      <c r="S62" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
@@ -5653,7 +5921,7 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="6" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>41</v>
@@ -5667,7 +5935,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="7">
-        <v>2026090072</v>
+        <v>2026090392</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5676,42 +5944,42 @@
         <v>29</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="N63" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O63" s="7" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="P63" s="7"/>
       <c r="Q63" s="7"/>
       <c r="R63" s="7">
-        <v>23897</v>
+        <v>0</v>
       </c>
       <c r="S63" s="7"/>
       <c r="T63" s="7"/>
@@ -5721,7 +5989,7 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="8" t="s">
-        <v>50</v>
+        <v>268</v>
       </c>
       <c r="AA63" s="7" t="s">
         <v>41</v>
@@ -5735,7 +6003,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>2026090593</v>
+        <v>2026090309</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -5744,28 +6012,24 @@
         <v>29</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>51</v>
+        <v>269</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
       <c r="L64" s="6" t="s">
-        <v>177</v>
+        <v>91</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>272</v>
@@ -5774,16 +6038,16 @@
         <v>273</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P64" s="3"/>
-      <c r="Q64" s="3">
-        <v>586</v>
-      </c>
+      <c r="Q64" s="3"/>
       <c r="R64" s="3">
-        <v>43605</v>
-      </c>
-      <c r="S64" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -5791,7 +6055,7 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="6" t="s">
-        <v>236</v>
+        <v>105</v>
       </c>
       <c r="AA64" s="3" t="s">
         <v>41</v>
@@ -5805,7 +6069,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026090406</v>
+        <v>2026090919</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -5814,52 +6078,50 @@
         <v>29</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>70</v>
+        <v>274</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="K65" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="J65" s="7"/>
+      <c r="K65" s="7"/>
       <c r="L65" s="8" t="s">
-        <v>276</v>
+        <v>91</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>277</v>
+        <v>158</v>
       </c>
       <c r="N65" s="8" t="s">
-        <v>278</v>
+        <v>159</v>
       </c>
       <c r="O65" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P65" s="7"/>
       <c r="Q65" s="7"/>
       <c r="R65" s="7">
-        <v>124253</v>
+        <v>0</v>
       </c>
       <c r="S65" s="7"/>
-      <c r="T65" s="7"/>
+      <c r="T65" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="U65" s="7"/>
       <c r="V65" s="7"/>
       <c r="W65" s="7"/>
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="8" t="s">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="AA65" s="7" t="s">
         <v>41</v>
@@ -5873,7 +6135,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026090078</v>
+        <v>2026090708</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -5882,44 +6144,42 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>255</v>
+        <v>129</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
       <c r="L66" s="6" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P66" s="3"/>
       <c r="Q66" s="3"/>
       <c r="R66" s="3">
-        <v>1150</v>
-      </c>
-      <c r="S66" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -5927,7 +6187,7 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="6" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>41</v>
@@ -5941,7 +6201,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="7">
-        <v>2026090076</v>
+        <v>2026090949</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -5950,42 +6210,46 @@
         <v>29</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>140</v>
+        <v>269</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>275</v>
+        <v>54</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>242</v>
+        <v>37</v>
       </c>
       <c r="M67" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="N67" s="8" t="s">
         <v>283</v>
-      </c>
-      <c r="N67" s="8" t="s">
-        <v>284</v>
       </c>
       <c r="O67" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P67" s="7"/>
-      <c r="Q67" s="7"/>
+      <c r="P67" s="7">
+        <v>2781</v>
+      </c>
+      <c r="Q67" s="7">
+        <v>3758</v>
+      </c>
       <c r="R67" s="7">
-        <v>6813</v>
+        <v>18574</v>
       </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7"/>
@@ -5995,7 +6259,7 @@
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
       <c r="Z67" s="8" t="s">
-        <v>50</v>
+        <v>284</v>
       </c>
       <c r="AA67" s="7" t="s">
         <v>41</v>
@@ -6009,7 +6273,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>2026090477</v>
+        <v>2026090240</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -6018,22 +6282,22 @@
         <v>29</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>226</v>
+        <v>145</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>285</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>190</v>
+        <v>54</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>36</v>
@@ -6045,17 +6309,17 @@
         <v>287</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>288</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="P68" s="3"/>
       <c r="Q68" s="3">
-        <v>2506</v>
+        <v>1900</v>
       </c>
       <c r="R68" s="3">
-        <v>6417</v>
+        <v>28500</v>
       </c>
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
@@ -6065,7 +6329,7 @@
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="6" t="s">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="AA68" s="3" t="s">
         <v>41</v>
@@ -6079,7 +6343,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026090465</v>
+        <v>2026090948</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -6088,28 +6352,28 @@
         <v>29</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>289</v>
+        <v>54</v>
       </c>
       <c r="K69" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>290</v>
+        <v>37</v>
       </c>
       <c r="M69" s="8" t="s">
         <v>291</v>
@@ -6120,10 +6384,14 @@
       <c r="O69" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
+      <c r="P69" s="7">
+        <v>983</v>
+      </c>
+      <c r="Q69" s="7">
+        <v>1988</v>
+      </c>
       <c r="R69" s="7">
-        <v>53932</v>
+        <v>13240</v>
       </c>
       <c r="S69" s="7"/>
       <c r="T69" s="7"/>
@@ -6133,7 +6401,7 @@
       <c r="X69" s="7"/>
       <c r="Y69" s="7"/>
       <c r="Z69" s="8" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="AA69" s="7" t="s">
         <v>41</v>
@@ -6147,7 +6415,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026090432</v>
+        <v>2026090256</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -6156,42 +6424,44 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>32</v>
+        <v>189</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>293</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>289</v>
+        <v>54</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>276</v>
+        <v>55</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>294</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
+      <c r="Q70" s="3">
+        <v>6432</v>
+      </c>
       <c r="R70" s="3">
-        <v>30234</v>
+        <v>770</v>
       </c>
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
@@ -6201,7 +6471,7 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="6" t="s">
-        <v>236</v>
+        <v>49</v>
       </c>
       <c r="AA70" s="3" t="s">
         <v>41</v>
@@ -6215,7 +6485,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026090428</v>
+        <v>2026090405</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -6224,42 +6494,44 @@
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G71" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="H71" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="H71" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="I71" s="7" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>289</v>
+        <v>54</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>276</v>
+        <v>55</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="O71" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P71" s="7"/>
-      <c r="Q71" s="7"/>
+      <c r="Q71" s="7">
+        <v>770</v>
+      </c>
       <c r="R71" s="7">
-        <v>130586</v>
+        <v>6432</v>
       </c>
       <c r="S71" s="7"/>
       <c r="T71" s="7"/>
@@ -6269,7 +6541,7 @@
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
       <c r="Z71" s="8" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="AA71" s="7" t="s">
         <v>41</v>
@@ -6283,7 +6555,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026090407</v>
+        <v>2026090813</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6292,52 +6564,56 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>289</v>
+        <v>54</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>276</v>
+        <v>55</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P72" s="3"/>
-      <c r="Q72" s="3"/>
+      <c r="Q72" s="3">
+        <v>770</v>
+      </c>
       <c r="R72" s="3">
-        <v>280656</v>
+        <v>6432</v>
       </c>
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
-      <c r="W72" s="3"/>
+      <c r="W72" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
       <c r="Z72" s="6" t="s">
-        <v>236</v>
+        <v>298</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>41</v>
@@ -6351,7 +6627,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7">
-        <v>2026090430</v>
+        <v>2026090588</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -6360,34 +6636,34 @@
         <v>29</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>289</v>
+        <v>198</v>
       </c>
       <c r="K73" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>276</v>
+        <v>213</v>
       </c>
       <c r="M73" s="8" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="N73" s="8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="O73" s="7" t="s">
         <v>39</v>
@@ -6395,7 +6671,7 @@
       <c r="P73" s="7"/>
       <c r="Q73" s="7"/>
       <c r="R73" s="7">
-        <v>212550</v>
+        <v>4146</v>
       </c>
       <c r="S73" s="7"/>
       <c r="T73" s="7"/>
@@ -6405,7 +6681,7 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="8" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="AA73" s="7" t="s">
         <v>41</v>
@@ -6419,7 +6695,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>2026090466</v>
+        <v>2026090071</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -6428,42 +6704,42 @@
         <v>29</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>32</v>
+        <v>295</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>303</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>289</v>
+        <v>198</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3">
-        <v>212550</v>
+        <v>3953</v>
       </c>
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
@@ -6473,7 +6749,7 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
       <c r="Z74" s="6" t="s">
-        <v>306</v>
+        <v>49</v>
       </c>
       <c r="AA74" s="3" t="s">
         <v>41</v>
@@ -6487,7 +6763,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="7">
-        <v>2026090639</v>
+        <v>2026090603</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
@@ -6496,42 +6772,42 @@
         <v>29</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>212</v>
+        <v>100</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>307</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K75" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L75" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M75" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="M75" s="8" t="s">
+      <c r="N75" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="N75" s="8" t="s">
-        <v>310</v>
-      </c>
       <c r="O75" s="7" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="P75" s="7"/>
       <c r="Q75" s="7"/>
       <c r="R75" s="7">
-        <v>162634</v>
+        <v>10</v>
       </c>
       <c r="S75" s="7"/>
       <c r="T75" s="7"/>
@@ -6541,7 +6817,7 @@
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
       <c r="Z75" s="8" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="AA75" s="7" t="s">
         <v>41</v>
@@ -6555,7 +6831,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="3">
-        <v>2026090586</v>
+        <v>2026090936</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
@@ -6564,34 +6840,34 @@
         <v>29</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>39</v>
@@ -6599,7 +6875,7 @@
       <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3">
-        <v>51037</v>
+        <v>59578</v>
       </c>
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
@@ -6609,7 +6885,7 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="6" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>41</v>
@@ -6623,7 +6899,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="7">
-        <v>2026090585</v>
+        <v>2026090937</v>
       </c>
       <c r="C77" s="7">
         <v>1</v>
@@ -6632,31 +6908,31 @@
         <v>29</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>225</v>
+        <v>279</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>234</v>
+        <v>81</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>240</v>
+        <v>313</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K77" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N77" s="8" t="s">
         <v>316</v>
@@ -6667,7 +6943,7 @@
       <c r="P77" s="7"/>
       <c r="Q77" s="7"/>
       <c r="R77" s="7">
-        <v>508479</v>
+        <v>94826</v>
       </c>
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
@@ -6677,7 +6953,7 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="8" t="s">
-        <v>236</v>
+        <v>284</v>
       </c>
       <c r="AA77" s="7" t="s">
         <v>41</v>
@@ -6691,7 +6967,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>2026090635</v>
+        <v>2026090939</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -6700,42 +6976,44 @@
         <v>29</v>
       </c>
       <c r="E78" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="J78" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="K78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="H78" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I78" s="3" t="s">
+      <c r="M78" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="M78" s="6" t="s">
+      <c r="N78" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="N78" s="6" t="s">
-        <v>321</v>
-      </c>
       <c r="O78" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3">
-        <v>0</v>
-      </c>
-      <c r="S78" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>207942</v>
+      </c>
+      <c r="S78" s="3"/>
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
@@ -6743,7 +7021,7 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
       <c r="Z78" s="6" t="s">
-        <v>90</v>
+        <v>284</v>
       </c>
       <c r="AA78" s="3" t="s">
         <v>41</v>
@@ -6757,7 +7035,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="7">
-        <v>2026090469</v>
+        <v>2026090943</v>
       </c>
       <c r="C79" s="7">
         <v>1</v>
@@ -6766,42 +7044,42 @@
         <v>29</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>317</v>
+        <v>279</v>
       </c>
       <c r="F79" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="J79" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="K79" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="H79" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="K79" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="L79" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="M79" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O79" s="7" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="P79" s="7"/>
       <c r="Q79" s="7"/>
       <c r="R79" s="7">
-        <v>0</v>
+        <v>225561</v>
       </c>
       <c r="S79" s="7"/>
       <c r="T79" s="7"/>
@@ -6811,19 +7089,21 @@
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
       <c r="Z79" s="8" t="s">
-        <v>322</v>
+        <v>284</v>
       </c>
       <c r="AA79" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AB79" s="7"/>
+      <c r="AB79" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:28">
       <c r="A80" s="3">
         <v>78</v>
       </c>
       <c r="B80" s="3">
-        <v>2026090634</v>
+        <v>2026090587</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
@@ -6832,24 +7112,28 @@
         <v>29</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>317</v>
+        <v>279</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
+      <c r="J80" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L80" s="6" t="s">
-        <v>80</v>
+        <v>213</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>326</v>
@@ -6858,16 +7142,14 @@
         <v>327</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="P80" s="3"/>
       <c r="Q80" s="3"/>
       <c r="R80" s="3">
-        <v>0</v>
-      </c>
-      <c r="S80" s="3" t="s">
-        <v>41</v>
-      </c>
+        <v>63226</v>
+      </c>
+      <c r="S80" s="3"/>
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
@@ -6875,47 +7157,2239 @@
       <c r="X80" s="3"/>
       <c r="Y80" s="3"/>
       <c r="Z80" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA80" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28">
+      <c r="A81" s="7">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7">
+        <v>2026090804</v>
+      </c>
+      <c r="C81" s="7">
+        <v>1</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="N81" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="O81" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="7">
+        <v>63226</v>
+      </c>
+      <c r="S81" s="7"/>
+      <c r="T81" s="7"/>
+      <c r="U81" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V81" s="7"/>
+      <c r="W81" s="7"/>
+      <c r="X81" s="7"/>
+      <c r="Y81" s="7"/>
+      <c r="Z81" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA81" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB81" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28">
+      <c r="A82" s="3">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3">
+        <v>2026090075</v>
+      </c>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3">
+        <v>11827</v>
+      </c>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA82" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB82" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28">
+      <c r="A83" s="7">
+        <v>81</v>
+      </c>
+      <c r="B83" s="7">
+        <v>2026090938</v>
+      </c>
+      <c r="C83" s="7">
+        <v>1</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="M83" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="N83" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="O83" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7">
+        <v>9801</v>
+      </c>
+      <c r="S83" s="7"/>
+      <c r="T83" s="7"/>
+      <c r="U83" s="7"/>
+      <c r="V83" s="7"/>
+      <c r="W83" s="7"/>
+      <c r="X83" s="7"/>
+      <c r="Y83" s="7"/>
+      <c r="Z83" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA83" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB83" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28">
+      <c r="A84" s="3">
+        <v>82</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2026090077</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3">
+        <v>49123</v>
+      </c>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
+      <c r="Z84" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA84" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28">
+      <c r="A85" s="7">
+        <v>83</v>
+      </c>
+      <c r="B85" s="7">
+        <v>2026090074</v>
+      </c>
+      <c r="C85" s="7">
+        <v>1</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="M85" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="N85" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="O85" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P85" s="7"/>
+      <c r="Q85" s="7"/>
+      <c r="R85" s="7">
+        <v>61971</v>
+      </c>
+      <c r="S85" s="7"/>
+      <c r="T85" s="7"/>
+      <c r="U85" s="7"/>
+      <c r="V85" s="7"/>
+      <c r="W85" s="7"/>
+      <c r="X85" s="7"/>
+      <c r="Y85" s="7"/>
+      <c r="Z85" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA85" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB85" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28">
+      <c r="A86" s="3">
+        <v>84</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2026090079</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3">
+        <v>39446</v>
+      </c>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28">
+      <c r="A87" s="7">
+        <v>85</v>
+      </c>
+      <c r="B87" s="7">
+        <v>2026090073</v>
+      </c>
+      <c r="C87" s="7">
+        <v>1</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="M87" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="N87" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="O87" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P87" s="7"/>
+      <c r="Q87" s="7"/>
+      <c r="R87" s="7">
+        <v>45148</v>
+      </c>
+      <c r="S87" s="7"/>
+      <c r="T87" s="7"/>
+      <c r="U87" s="7"/>
+      <c r="V87" s="7"/>
+      <c r="W87" s="7"/>
+      <c r="X87" s="7"/>
+      <c r="Y87" s="7"/>
+      <c r="Z87" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA87" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB87" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28">
+      <c r="A88" s="3">
+        <v>86</v>
+      </c>
+      <c r="B88" s="3">
+        <v>2026090072</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3">
+        <v>23897</v>
+      </c>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA88" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28">
+      <c r="A89" s="7">
+        <v>87</v>
+      </c>
+      <c r="B89" s="7">
+        <v>2026090593</v>
+      </c>
+      <c r="C89" s="7">
+        <v>1</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="K89" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M89" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="N89" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="O89" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P89" s="7"/>
+      <c r="Q89" s="7">
+        <v>586</v>
+      </c>
+      <c r="R89" s="7">
+        <v>43605</v>
+      </c>
+      <c r="S89" s="7"/>
+      <c r="T89" s="7"/>
+      <c r="U89" s="7"/>
+      <c r="V89" s="7"/>
+      <c r="W89" s="7"/>
+      <c r="X89" s="7"/>
+      <c r="Y89" s="7"/>
+      <c r="Z89" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA89" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB89" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28">
+      <c r="A90" s="3">
+        <v>88</v>
+      </c>
+      <c r="B90" s="3">
+        <v>2026090406</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3">
+        <v>124253</v>
+      </c>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA90" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB90" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28">
+      <c r="A91" s="7">
+        <v>89</v>
+      </c>
+      <c r="B91" s="7">
+        <v>2026090078</v>
+      </c>
+      <c r="C91" s="7">
+        <v>1</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="K91" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="M91" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="N91" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="O91" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="7"/>
+      <c r="R91" s="7">
+        <v>1150</v>
+      </c>
+      <c r="S91" s="7"/>
+      <c r="T91" s="7"/>
+      <c r="U91" s="7"/>
+      <c r="V91" s="7"/>
+      <c r="W91" s="7"/>
+      <c r="X91" s="7"/>
+      <c r="Y91" s="7"/>
+      <c r="Z91" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA91" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB91" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28">
+      <c r="A92" s="3">
         <v>90</v>
       </c>
-      <c r="AA80" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB80" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:28">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="10"/>
-      <c r="N81" s="10"/>
-      <c r="O81" s="9"/>
-      <c r="P81" s="9"/>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-      <c r="U81" s="9"/>
-      <c r="V81" s="9"/>
-      <c r="W81" s="9"/>
-      <c r="X81" s="9"/>
-      <c r="Y81" s="9"/>
-      <c r="Z81" s="10"/>
-      <c r="AA81" s="9" t="s">
+      <c r="B92" s="3">
+        <v>2026090076</v>
+      </c>
+      <c r="C92" s="3">
+        <v>1</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3">
+        <v>6813</v>
+      </c>
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+      <c r="Z92" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA92" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28">
+      <c r="A93" s="7">
+        <v>91</v>
+      </c>
+      <c r="B93" s="7">
+        <v>2026090477</v>
+      </c>
+      <c r="C93" s="7">
+        <v>1</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L93" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="M93" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="N93" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="O93" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7">
+        <v>2506</v>
+      </c>
+      <c r="R93" s="7">
+        <v>6417</v>
+      </c>
+      <c r="S93" s="7"/>
+      <c r="T93" s="7"/>
+      <c r="U93" s="7"/>
+      <c r="V93" s="7"/>
+      <c r="W93" s="7"/>
+      <c r="X93" s="7"/>
+      <c r="Y93" s="7"/>
+      <c r="Z93" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA93" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB93" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28">
+      <c r="A94" s="3">
+        <v>92</v>
+      </c>
+      <c r="B94" s="3">
+        <v>2026090465</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3">
+        <v>53932</v>
+      </c>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28">
+      <c r="A95" s="7">
+        <v>93</v>
+      </c>
+      <c r="B95" s="7">
+        <v>2026090432</v>
+      </c>
+      <c r="C95" s="7">
+        <v>1</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="K95" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="M95" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="N95" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="O95" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
+      <c r="R95" s="7">
+        <v>30234</v>
+      </c>
+      <c r="S95" s="7"/>
+      <c r="T95" s="7"/>
+      <c r="U95" s="7"/>
+      <c r="V95" s="7"/>
+      <c r="W95" s="7"/>
+      <c r="X95" s="7"/>
+      <c r="Y95" s="7"/>
+      <c r="Z95" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA95" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB95" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28">
+      <c r="A96" s="3">
+        <v>94</v>
+      </c>
+      <c r="B96" s="3">
+        <v>2026090428</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3">
+        <v>130586</v>
+      </c>
+      <c r="S96" s="3"/>
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+      <c r="X96" s="3"/>
+      <c r="Y96" s="3"/>
+      <c r="Z96" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA96" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28">
+      <c r="A97" s="7">
+        <v>95</v>
+      </c>
+      <c r="B97" s="7">
+        <v>2026090810</v>
+      </c>
+      <c r="C97" s="7">
+        <v>1</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="M97" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="N97" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="O97" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P97" s="7"/>
+      <c r="Q97" s="7"/>
+      <c r="R97" s="7">
+        <v>130586</v>
+      </c>
+      <c r="S97" s="7"/>
+      <c r="T97" s="7"/>
+      <c r="U97" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V97" s="7"/>
+      <c r="W97" s="7"/>
+      <c r="X97" s="7"/>
+      <c r="Y97" s="7"/>
+      <c r="Z97" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA97" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB97" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28">
+      <c r="A98" s="3">
+        <v>96</v>
+      </c>
+      <c r="B98" s="3">
+        <v>2026090407</v>
+      </c>
+      <c r="C98" s="3">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3">
+        <v>280656</v>
+      </c>
+      <c r="S98" s="3"/>
+      <c r="T98" s="3"/>
+      <c r="U98" s="3"/>
+      <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
+      <c r="X98" s="3"/>
+      <c r="Y98" s="3"/>
+      <c r="Z98" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA98" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28">
+      <c r="A99" s="7">
+        <v>97</v>
+      </c>
+      <c r="B99" s="7">
+        <v>2026090430</v>
+      </c>
+      <c r="C99" s="7">
+        <v>1</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="K99" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="M99" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="N99" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="O99" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P99" s="7"/>
+      <c r="Q99" s="7"/>
+      <c r="R99" s="7">
+        <v>212550</v>
+      </c>
+      <c r="S99" s="7"/>
+      <c r="T99" s="7"/>
+      <c r="U99" s="7"/>
+      <c r="V99" s="7"/>
+      <c r="W99" s="7"/>
+      <c r="X99" s="7"/>
+      <c r="Y99" s="7"/>
+      <c r="Z99" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA99" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB99" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28">
+      <c r="A100" s="3">
+        <v>98</v>
+      </c>
+      <c r="B100" s="3">
+        <v>2026090466</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3">
+        <v>212550</v>
+      </c>
+      <c r="S100" s="3"/>
+      <c r="T100" s="3"/>
+      <c r="U100" s="3"/>
+      <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
+      <c r="X100" s="3"/>
+      <c r="Y100" s="3"/>
+      <c r="Z100" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB100" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28">
+      <c r="A101" s="7">
+        <v>99</v>
+      </c>
+      <c r="B101" s="7">
+        <v>2026090808</v>
+      </c>
+      <c r="C101" s="7">
+        <v>1</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="K101" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="M101" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="N101" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="O101" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P101" s="7"/>
+      <c r="Q101" s="7"/>
+      <c r="R101" s="7">
+        <v>212550</v>
+      </c>
+      <c r="S101" s="7"/>
+      <c r="T101" s="7"/>
+      <c r="U101" s="7"/>
+      <c r="V101" s="7"/>
+      <c r="W101" s="7"/>
+      <c r="X101" s="7"/>
+      <c r="Y101" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z101" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="AA101" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB101" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28">
+      <c r="A102" s="3">
+        <v>100</v>
+      </c>
+      <c r="B102" s="3">
+        <v>2026090639</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L102" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3">
+        <v>162634</v>
+      </c>
+      <c r="S102" s="3"/>
+      <c r="T102" s="3"/>
+      <c r="U102" s="3"/>
+      <c r="V102" s="3"/>
+      <c r="W102" s="3"/>
+      <c r="X102" s="3"/>
+      <c r="Y102" s="3"/>
+      <c r="Z102" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28">
+      <c r="A103" s="7">
+        <v>101</v>
+      </c>
+      <c r="B103" s="7">
+        <v>2026090809</v>
+      </c>
+      <c r="C103" s="7">
+        <v>1</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="I103" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L103" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="M103" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="N103" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="O103" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P103" s="7"/>
+      <c r="Q103" s="7"/>
+      <c r="R103" s="7">
+        <v>160488</v>
+      </c>
+      <c r="S103" s="7"/>
+      <c r="T103" s="7"/>
+      <c r="U103" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V103" s="7"/>
+      <c r="W103" s="7"/>
+      <c r="X103" s="7"/>
+      <c r="Y103" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z103" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="AA103" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB103" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28">
+      <c r="A104" s="3">
+        <v>102</v>
+      </c>
+      <c r="B104" s="3">
+        <v>2026090586</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L104" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="O104" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3">
+        <v>51037</v>
+      </c>
+      <c r="S104" s="3"/>
+      <c r="T104" s="3"/>
+      <c r="U104" s="3"/>
+      <c r="V104" s="3"/>
+      <c r="W104" s="3"/>
+      <c r="X104" s="3"/>
+      <c r="Y104" s="3"/>
+      <c r="Z104" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA104" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB104" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28">
+      <c r="A105" s="7">
+        <v>103</v>
+      </c>
+      <c r="B105" s="7">
+        <v>2026090805</v>
+      </c>
+      <c r="C105" s="7">
+        <v>1</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G105" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="AB81" s="9">
-        <v>58</v>
+      <c r="H105" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L105" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M105" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="N105" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="O105" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P105" s="7"/>
+      <c r="Q105" s="7"/>
+      <c r="R105" s="7">
+        <v>51037</v>
+      </c>
+      <c r="S105" s="7"/>
+      <c r="T105" s="7"/>
+      <c r="U105" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V105" s="7"/>
+      <c r="W105" s="7"/>
+      <c r="X105" s="7"/>
+      <c r="Y105" s="7"/>
+      <c r="Z105" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA105" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB105" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28">
+      <c r="A106" s="3">
+        <v>104</v>
+      </c>
+      <c r="B106" s="3">
+        <v>2026090585</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L106" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+      <c r="R106" s="3">
+        <v>508479</v>
+      </c>
+      <c r="S106" s="3"/>
+      <c r="T106" s="3"/>
+      <c r="U106" s="3"/>
+      <c r="V106" s="3"/>
+      <c r="W106" s="3"/>
+      <c r="X106" s="3"/>
+      <c r="Y106" s="3"/>
+      <c r="Z106" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA106" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB106" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28">
+      <c r="A107" s="7">
+        <v>105</v>
+      </c>
+      <c r="B107" s="7">
+        <v>2026090806</v>
+      </c>
+      <c r="C107" s="7">
+        <v>1</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="J107" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M107" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="N107" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="O107" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P107" s="7"/>
+      <c r="Q107" s="7"/>
+      <c r="R107" s="7">
+        <v>508479</v>
+      </c>
+      <c r="S107" s="7"/>
+      <c r="T107" s="7"/>
+      <c r="U107" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="V107" s="7"/>
+      <c r="W107" s="7"/>
+      <c r="X107" s="7"/>
+      <c r="Y107" s="7"/>
+      <c r="Z107" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA107" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB107" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28">
+      <c r="A108" s="3">
+        <v>106</v>
+      </c>
+      <c r="B108" s="3">
+        <v>2026090807</v>
+      </c>
+      <c r="C108" s="3">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L108" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3">
+        <v>553221</v>
+      </c>
+      <c r="S108" s="3"/>
+      <c r="T108" s="3"/>
+      <c r="U108" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="V108" s="3"/>
+      <c r="W108" s="3"/>
+      <c r="X108" s="3"/>
+      <c r="Y108" s="3"/>
+      <c r="Z108" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="AA108" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB108" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28">
+      <c r="A109" s="7">
+        <v>107</v>
+      </c>
+      <c r="B109" s="7">
+        <v>2026090935</v>
+      </c>
+      <c r="C109" s="7">
+        <v>1</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I109" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="M109" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="N109" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="O109" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P109" s="7"/>
+      <c r="Q109" s="7"/>
+      <c r="R109" s="7">
+        <v>0</v>
+      </c>
+      <c r="S109" s="7"/>
+      <c r="T109" s="7"/>
+      <c r="U109" s="7"/>
+      <c r="V109" s="7"/>
+      <c r="W109" s="7"/>
+      <c r="X109" s="7"/>
+      <c r="Y109" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z109" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="AA109" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB109" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28">
+      <c r="A110" s="3">
+        <v>108</v>
+      </c>
+      <c r="B110" s="3">
+        <v>2026090469</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L110" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="O110" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P110" s="3"/>
+      <c r="Q110" s="3"/>
+      <c r="R110" s="3">
+        <v>0</v>
+      </c>
+      <c r="S110" s="3"/>
+      <c r="T110" s="3"/>
+      <c r="U110" s="3"/>
+      <c r="V110" s="3"/>
+      <c r="W110" s="3"/>
+      <c r="X110" s="3"/>
+      <c r="Y110" s="3"/>
+      <c r="Z110" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="AA110" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB110" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28">
+      <c r="A111" s="7">
+        <v>109</v>
+      </c>
+      <c r="B111" s="7">
+        <v>2026090635</v>
+      </c>
+      <c r="C111" s="7">
+        <v>1</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M111" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="N111" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="O111" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P111" s="7"/>
+      <c r="Q111" s="7"/>
+      <c r="R111" s="7">
+        <v>0</v>
+      </c>
+      <c r="S111" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="T111" s="7"/>
+      <c r="U111" s="7"/>
+      <c r="V111" s="7"/>
+      <c r="W111" s="7"/>
+      <c r="X111" s="7"/>
+      <c r="Y111" s="7"/>
+      <c r="Z111" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA111" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB111" s="7"/>
+    </row>
+    <row r="112" spans="1:28">
+      <c r="A112" s="3">
+        <v>110</v>
+      </c>
+      <c r="B112" s="3">
+        <v>2026090634</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J112" s="3"/>
+      <c r="K112" s="3"/>
+      <c r="L112" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M112" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="N112" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P112" s="3"/>
+      <c r="Q112" s="3"/>
+      <c r="R112" s="3">
+        <v>0</v>
+      </c>
+      <c r="S112" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T112" s="3"/>
+      <c r="U112" s="3"/>
+      <c r="V112" s="3"/>
+      <c r="W112" s="3"/>
+      <c r="X112" s="3"/>
+      <c r="Y112" s="3"/>
+      <c r="Z112" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA112" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB112" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28">
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="9"/>
+      <c r="H113" s="9"/>
+      <c r="I113" s="9"/>
+      <c r="J113" s="9"/>
+      <c r="K113" s="9"/>
+      <c r="L113" s="10"/>
+      <c r="M113" s="10"/>
+      <c r="N113" s="10"/>
+      <c r="O113" s="9"/>
+      <c r="P113" s="9"/>
+      <c r="Q113" s="9"/>
+      <c r="R113" s="9"/>
+      <c r="S113" s="9"/>
+      <c r="T113" s="9"/>
+      <c r="U113" s="9"/>
+      <c r="V113" s="9"/>
+      <c r="W113" s="9"/>
+      <c r="X113" s="9"/>
+      <c r="Y113" s="9"/>
+      <c r="Z113" s="10"/>
+      <c r="AA113" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="AB113" s="9">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
